--- a/exp2.xlsx
+++ b/exp2.xlsx
@@ -8,17 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\3sem_git\Algs_and_data_structures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E211D7B9-42E6-47C7-8657-E97BC6336DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0803815E-F8D7-4123-BA6B-6DB05F0EFC8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="main" sheetId="1" r:id="rId1"/>
-    <sheet name="graph" sheetId="4" r:id="rId2"/>
+    <sheet name="random" sheetId="1" r:id="rId1"/>
+    <sheet name="r_gr" sheetId="4" r:id="rId2"/>
+    <sheet name="sorted" sheetId="5" r:id="rId3"/>
+    <sheet name="s_gr" sheetId="6" r:id="rId4"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId3"/>
-  </externalReferences>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="10">
   <si>
     <t>N</t>
   </si>
@@ -145,9 +144,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -155,7 +154,106 @@
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -349,7 +447,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>main!$C$2</c:f>
+              <c:f>random!$C$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -372,7 +470,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>main!$B$3:$B$52</c:f>
+              <c:f>random!$B$3:$B$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="50"/>
@@ -531,7 +629,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>main!$C$3:$C$52</c:f>
+              <c:f>random!$C$3:$C$52</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="50"/>
@@ -700,7 +798,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>main!$G$2</c:f>
+              <c:f>random!$G$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -723,7 +821,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>main!$B$3:$B$52</c:f>
+              <c:f>random!$B$3:$B$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="50"/>
@@ -882,7 +980,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>main!$G$3:$G$52</c:f>
+              <c:f>random!$G$3:$G$52</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="50"/>
@@ -1051,7 +1149,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>main!$K$2</c:f>
+              <c:f>random!$K$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1074,7 +1172,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>main!$B$3:$B$52</c:f>
+              <c:f>random!$B$3:$B$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="50"/>
@@ -1233,7 +1331,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>main!$K$3:$K$52</c:f>
+              <c:f>random!$K$3:$K$52</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="50"/>
@@ -1673,7 +1771,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>main!$D$2</c:f>
+              <c:f>random!$D$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1696,7 +1794,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>main!$B$3:$B$52</c:f>
+              <c:f>random!$B$3:$B$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="50"/>
@@ -1855,7 +1953,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>main!$D$3:$D$52</c:f>
+              <c:f>random!$D$3:$D$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="50"/>
@@ -2024,7 +2122,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>main!$H$2</c:f>
+              <c:f>random!$H$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2047,7 +2145,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>main!$B$3:$B$52</c:f>
+              <c:f>random!$B$3:$B$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="50"/>
@@ -2206,7 +2304,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>main!$H$3:$H$52</c:f>
+              <c:f>random!$H$3:$H$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="50"/>
@@ -2375,7 +2473,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>main!$L$2</c:f>
+              <c:f>random!$L$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2398,7 +2496,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>main!$B$3:$B$52</c:f>
+              <c:f>random!$B$3:$B$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="50"/>
@@ -2557,7 +2655,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>main!$L$3:$L$52</c:f>
+              <c:f>random!$L$3:$L$52</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="50"/>
@@ -2916,6 +3014,2653 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Copy</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>sorted!$C$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Copy q</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>sorted!$B$3:$B$52</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17000</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18000</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19000</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20000</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21000</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22000</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23000</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24000</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25000</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26000</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27000</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28000</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29000</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30000</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>31000</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>32000</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33000</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34000</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35000</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36000</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37000</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>38000</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>39000</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>40000</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>41000</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>42000</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>43000</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>44000</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45000</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46000</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>47000</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>48000</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>49000</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>50000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>sorted!$C$3:$C$52</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>11998</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>13998</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>15998</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>17998</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>19998</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>21998</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>23998</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>25998</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>27998</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>29998</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>31998</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>33998</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>35998</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>37998</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>39998</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>41998</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>43998</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>45998</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>47998</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>49998</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>51998</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>53998</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>55998</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>57998</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>59998</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>61998</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>63998</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>65998</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>67998</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>69998</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>71998</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>73998</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>75998</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>77998</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>79998</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>81998</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>83998</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>85998</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>87998</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>89998</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>91998</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>93998</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>95998</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>97998</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>99998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5676-435C-B67A-9BD7276D8773}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>sorted!$G$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Copy sh</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>sorted!$B$3:$B$52</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17000</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18000</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19000</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20000</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21000</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22000</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23000</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24000</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25000</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26000</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27000</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28000</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29000</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30000</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>31000</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>32000</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33000</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34000</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35000</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36000</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37000</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>38000</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>39000</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>40000</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>41000</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>42000</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>43000</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>44000</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45000</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46000</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>47000</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>48000</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>49000</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>50000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>sorted!$G$3:$G$52</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5676-435C-B67A-9BD7276D8773}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>sorted!$K$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Copy ins</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>sorted!$B$3:$B$52</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17000</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18000</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19000</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20000</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21000</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22000</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23000</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24000</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25000</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26000</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27000</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28000</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29000</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30000</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>31000</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>32000</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33000</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34000</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35000</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36000</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37000</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>38000</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>39000</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>40000</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>41000</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>42000</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>43000</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>44000</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45000</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46000</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>47000</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>48000</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>49000</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>50000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>sorted!$K$3:$K$52</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5998</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="General">
+                  <c:v>7998</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="General">
+                  <c:v>9998</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="General">
+                  <c:v>11998</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="General">
+                  <c:v>13998</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="General">
+                  <c:v>15998</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="General">
+                  <c:v>17998</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="General">
+                  <c:v>19998</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="General">
+                  <c:v>21998</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="General">
+                  <c:v>23998</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="General">
+                  <c:v>25998</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="General">
+                  <c:v>27998</c:v>
+                </c:pt>
+                <c:pt idx="14" formatCode="General">
+                  <c:v>29998</c:v>
+                </c:pt>
+                <c:pt idx="15" formatCode="General">
+                  <c:v>31998</c:v>
+                </c:pt>
+                <c:pt idx="16" formatCode="General">
+                  <c:v>33998</c:v>
+                </c:pt>
+                <c:pt idx="17" formatCode="General">
+                  <c:v>35998</c:v>
+                </c:pt>
+                <c:pt idx="18" formatCode="General">
+                  <c:v>37998</c:v>
+                </c:pt>
+                <c:pt idx="19" formatCode="General">
+                  <c:v>39998</c:v>
+                </c:pt>
+                <c:pt idx="20" formatCode="General">
+                  <c:v>41998</c:v>
+                </c:pt>
+                <c:pt idx="21" formatCode="General">
+                  <c:v>43998</c:v>
+                </c:pt>
+                <c:pt idx="22" formatCode="General">
+                  <c:v>45998</c:v>
+                </c:pt>
+                <c:pt idx="23" formatCode="General">
+                  <c:v>47998</c:v>
+                </c:pt>
+                <c:pt idx="24" formatCode="General">
+                  <c:v>49998</c:v>
+                </c:pt>
+                <c:pt idx="25" formatCode="General">
+                  <c:v>51998</c:v>
+                </c:pt>
+                <c:pt idx="26" formatCode="General">
+                  <c:v>53998</c:v>
+                </c:pt>
+                <c:pt idx="27" formatCode="General">
+                  <c:v>55998</c:v>
+                </c:pt>
+                <c:pt idx="28" formatCode="General">
+                  <c:v>57998</c:v>
+                </c:pt>
+                <c:pt idx="29" formatCode="General">
+                  <c:v>59998</c:v>
+                </c:pt>
+                <c:pt idx="30" formatCode="General">
+                  <c:v>61998</c:v>
+                </c:pt>
+                <c:pt idx="31" formatCode="General">
+                  <c:v>63998</c:v>
+                </c:pt>
+                <c:pt idx="32" formatCode="General">
+                  <c:v>65998</c:v>
+                </c:pt>
+                <c:pt idx="33" formatCode="General">
+                  <c:v>67998</c:v>
+                </c:pt>
+                <c:pt idx="34" formatCode="General">
+                  <c:v>69998</c:v>
+                </c:pt>
+                <c:pt idx="35" formatCode="General">
+                  <c:v>71998</c:v>
+                </c:pt>
+                <c:pt idx="36" formatCode="General">
+                  <c:v>73998</c:v>
+                </c:pt>
+                <c:pt idx="37" formatCode="General">
+                  <c:v>75998</c:v>
+                </c:pt>
+                <c:pt idx="38" formatCode="General">
+                  <c:v>77998</c:v>
+                </c:pt>
+                <c:pt idx="39" formatCode="General">
+                  <c:v>79998</c:v>
+                </c:pt>
+                <c:pt idx="40" formatCode="General">
+                  <c:v>81998</c:v>
+                </c:pt>
+                <c:pt idx="41" formatCode="General">
+                  <c:v>83998</c:v>
+                </c:pt>
+                <c:pt idx="42" formatCode="General">
+                  <c:v>85998</c:v>
+                </c:pt>
+                <c:pt idx="43" formatCode="General">
+                  <c:v>87998</c:v>
+                </c:pt>
+                <c:pt idx="44" formatCode="General">
+                  <c:v>89998</c:v>
+                </c:pt>
+                <c:pt idx="45" formatCode="General">
+                  <c:v>91998</c:v>
+                </c:pt>
+                <c:pt idx="46" formatCode="General">
+                  <c:v>93998</c:v>
+                </c:pt>
+                <c:pt idx="47" formatCode="General">
+                  <c:v>95998</c:v>
+                </c:pt>
+                <c:pt idx="48" formatCode="General">
+                  <c:v>97998</c:v>
+                </c:pt>
+                <c:pt idx="49" formatCode="General">
+                  <c:v>99998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-5676-435C-B67A-9BD7276D8773}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="545024143"/>
+        <c:axId val="545033743"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="545024143"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="545033743"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="545033743"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="545024143"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Compare</a:t>
+            </a:r>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>sorted!$D$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Compare q</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>sorted!$B$3:$B$52</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17000</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18000</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19000</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20000</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21000</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22000</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23000</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24000</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25000</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26000</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27000</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28000</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29000</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30000</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>31000</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>32000</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33000</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34000</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35000</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36000</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37000</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>38000</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>39000</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>40000</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>41000</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>42000</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>43000</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>44000</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45000</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46000</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>47000</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>48000</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>49000</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>50000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>sorted!$D$3:$D$52</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11999</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12999</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14999</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15999</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18999</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19999</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20999</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>21999</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>22999</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>23999</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>24999</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>25999</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26999</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>27999</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>28999</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>29999</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>30999</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>31999</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>32999</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>33999</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>34999</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>35999</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>36999</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>37999</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>38999</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>39999</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>40999</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>41999</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>42999</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>43999</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>44999</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>45999</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46999</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>47999</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>48999</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>49999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B2BC-4B6A-85FF-5D5CA47E519C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>sorted!$H$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Compare sh</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>sorted!$B$3:$B$52</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17000</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18000</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19000</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20000</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21000</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22000</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23000</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24000</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25000</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26000</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27000</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28000</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29000</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30000</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>31000</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>32000</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33000</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34000</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35000</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36000</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37000</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>38000</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>39000</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>40000</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>41000</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>42000</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>43000</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>44000</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45000</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46000</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>47000</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>48000</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>49000</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>50000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>sorted!$H$3:$H$52</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>500500</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2001000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4501500</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8002000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12502500</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>18003000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>24503500</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>32004000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>40504500</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>50005000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>60505500</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>72006000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>84506500</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>98007000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>112507500</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>128008000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>144508500</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>162009000</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>180509500</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>200010000</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>220510500</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>242011000</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>264511500</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>288012000</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>312512500</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>338013000</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>364513500</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>392014000</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>420514500</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>450015000</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>480515500</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>512016000</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>544516500</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>578017000</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>612517500</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>648018000</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>684518500</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>722019000</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>760519500</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>800020000</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>840520500</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>882021000</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>924521500</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>968022000</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1012522500</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1058023000</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1104523500</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1152024000</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1200524500</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1250025000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-B2BC-4B6A-85FF-5D5CA47E519C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>sorted!$L$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Compare ins</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>sorted!$B$3:$B$52</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17000</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18000</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19000</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20000</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21000</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22000</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23000</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24000</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25000</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26000</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27000</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28000</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29000</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30000</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>31000</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>32000</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33000</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34000</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35000</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36000</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37000</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>38000</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>39000</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>40000</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>41000</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>42000</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>43000</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>44000</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45000</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46000</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>47000</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>48000</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>49000</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>50000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>sorted!$L$3:$L$52</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11999</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12999</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14999</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15999</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18999</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19999</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20999</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>21999</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>22999</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>23999</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>24999</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>25999</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26999</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>27999</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>28999</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>29999</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>30999</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>31999</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>32999</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>33999</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>34999</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>35999</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>36999</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>37999</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>38999</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>39999</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>40999</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>41999</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>42999</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>43999</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>44999</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>45999</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46999</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>47999</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>48999</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>4999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-B2BC-4B6A-85FF-5D5CA47E519C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="545023183"/>
+        <c:axId val="545021263"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="545023183"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="545021263"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="545021263"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="545023183"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -2996,6 +5741,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
@@ -3513,6 +6338,1038 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -4109,436 +7966,85 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="insert"/>
-      <sheetName val="shaker"/>
-      <sheetName val="quick"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2">
-        <row r="1">
-          <cell r="A1" t="str">
-            <v>N</v>
-          </cell>
-          <cell r="B1" t="str">
-            <v>Copy</v>
-          </cell>
-          <cell r="C1" t="str">
-            <v>Compare</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="B2">
-            <v>6915</v>
-          </cell>
-          <cell r="C2">
-            <v>22584</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3">
-            <v>16128</v>
-          </cell>
-          <cell r="C3">
-            <v>50847</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="B4">
-            <v>26358</v>
-          </cell>
-          <cell r="C4">
-            <v>79286</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="B5">
-            <v>38004</v>
-          </cell>
-          <cell r="C5">
-            <v>110717</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="B6">
-            <v>50103</v>
-          </cell>
-          <cell r="C6">
-            <v>141341</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7">
-            <v>61878</v>
-          </cell>
-          <cell r="C7">
-            <v>181355</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="B8">
-            <v>75156</v>
-          </cell>
-          <cell r="C8">
-            <v>207415</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="B9">
-            <v>88884</v>
-          </cell>
-          <cell r="C9">
-            <v>239889</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="B10">
-            <v>101175</v>
-          </cell>
-          <cell r="C10">
-            <v>277729</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="B11">
-            <v>116331</v>
-          </cell>
-          <cell r="C11">
-            <v>302706</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="B12">
-            <v>129855</v>
-          </cell>
-          <cell r="C12">
-            <v>346704</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="B13">
-            <v>143931</v>
-          </cell>
-          <cell r="C13">
-            <v>383609</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="B14">
-            <v>157776</v>
-          </cell>
-          <cell r="C14">
-            <v>419165</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="B15">
-            <v>173169</v>
-          </cell>
-          <cell r="C15">
-            <v>450403</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="B16">
-            <v>186552</v>
-          </cell>
-          <cell r="C16">
-            <v>489567</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="B17">
-            <v>203172</v>
-          </cell>
-          <cell r="C17">
-            <v>509810</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="B18">
-            <v>216915</v>
-          </cell>
-          <cell r="C18">
-            <v>553378</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="B19">
-            <v>233478</v>
-          </cell>
-          <cell r="C19">
-            <v>576831</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="B20">
-            <v>249651</v>
-          </cell>
-          <cell r="C20">
-            <v>620178</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="B21">
-            <v>264129</v>
-          </cell>
-          <cell r="C21">
-            <v>652860</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="B22">
-            <v>275535</v>
-          </cell>
-          <cell r="C22">
-            <v>709974</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="B23">
-            <v>295818</v>
-          </cell>
-          <cell r="C23">
-            <v>744431</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="B24">
-            <v>312822</v>
-          </cell>
-          <cell r="C24">
-            <v>762423</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="B25">
-            <v>326457</v>
-          </cell>
-          <cell r="C25">
-            <v>804992</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="B26">
-            <v>340827</v>
-          </cell>
-          <cell r="C26">
-            <v>842872</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="B27">
-            <v>358014</v>
-          </cell>
-          <cell r="C27">
-            <v>885077</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="B28">
-            <v>377871</v>
-          </cell>
-          <cell r="C28">
-            <v>899914</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="B29">
-            <v>389073</v>
-          </cell>
-          <cell r="C29">
-            <v>976657</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="B30">
-            <v>403410</v>
-          </cell>
-          <cell r="C30">
-            <v>1018053</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="B31">
-            <v>418812</v>
-          </cell>
-          <cell r="C31">
-            <v>1052939</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="B32">
-            <v>438408</v>
-          </cell>
-          <cell r="C32">
-            <v>1066456</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="B33">
-            <v>457938</v>
-          </cell>
-          <cell r="C33">
-            <v>1093157</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="B34">
-            <v>473919</v>
-          </cell>
-          <cell r="C34">
-            <v>1125782</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="B35">
-            <v>485010</v>
-          </cell>
-          <cell r="C35">
-            <v>1205095</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="B36">
-            <v>504888</v>
-          </cell>
-          <cell r="C36">
-            <v>1215717</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="B37">
-            <v>517818</v>
-          </cell>
-          <cell r="C37">
-            <v>1284504</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="B38">
-            <v>537942</v>
-          </cell>
-          <cell r="C38">
-            <v>1314310</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="B39">
-            <v>553212</v>
-          </cell>
-          <cell r="C39">
-            <v>1355086</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="B40">
-            <v>566037</v>
-          </cell>
-          <cell r="C40">
-            <v>1407971</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="B41">
-            <v>592452</v>
-          </cell>
-          <cell r="C41">
-            <v>1393180</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="B42">
-            <v>605139</v>
-          </cell>
-          <cell r="C42">
-            <v>1468096</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="B43">
-            <v>623622</v>
-          </cell>
-          <cell r="C43">
-            <v>1510350</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="B44">
-            <v>635223</v>
-          </cell>
-          <cell r="C44">
-            <v>1564793</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="B45">
-            <v>655665</v>
-          </cell>
-          <cell r="C45">
-            <v>1570611</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="B46">
-            <v>671139</v>
-          </cell>
-          <cell r="C46">
-            <v>1618058</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="B47">
-            <v>693852</v>
-          </cell>
-          <cell r="C47">
-            <v>1643349</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="B48">
-            <v>705540</v>
-          </cell>
-          <cell r="C48">
-            <v>1707876</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="B49">
-            <v>725127</v>
-          </cell>
-          <cell r="C49">
-            <v>1728246</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="B50">
-            <v>747039</v>
-          </cell>
-          <cell r="C50">
-            <v>1743993</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="B51">
-            <v>764073</v>
-          </cell>
-          <cell r="C51">
-            <v>1782257</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Диаграмма 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5ED18BB-B07E-4BFF-93EC-09086F395264}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>45720</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>594360</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Диаграмма 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B183484A-CB40-4067-814E-1E75740EE8D2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4546,7 +8052,7 @@
   <autoFilter ref="F2:H53" xr:uid="{12DBA126-0BED-484C-AA50-D6AE7A611FC4}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{609707E7-BB94-42A5-917D-9570B5AC7EEF}" name="N"/>
-    <tableColumn id="2" xr3:uid="{65B1B6C8-8ACD-417E-A7A0-594CC47A6D37}" name="Copy sh" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{65B1B6C8-8ACD-417E-A7A0-594CC47A6D37}" name="Copy sh" dataDxfId="9"/>
     <tableColumn id="3" xr3:uid="{F893E8C0-37FA-4D96-8689-B68BE51E2DFE}" name="Compare sh"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4554,12 +8060,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{3A419A4E-1F00-42E1-A1D0-7871938F171F}" name="Таблица7" displayName="Таблица7" ref="B2:D52" totalsRowShown="0" tableBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{3A419A4E-1F00-42E1-A1D0-7871938F171F}" name="Таблица7" displayName="Таблица7" ref="B2:D52" totalsRowShown="0" tableBorderDxfId="8">
   <autoFilter ref="B2:D52" xr:uid="{3A419A4E-1F00-42E1-A1D0-7871938F171F}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{C1BDC60F-4A13-494C-A180-955CEE5697F5}" name="N" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{1B7691C3-923C-4E01-92E9-BAD16478DB72}" name="Copy q" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{DE5D2A1C-D75F-491A-98D0-A233B66BB08C}" name="Compare q" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{C1BDC60F-4A13-494C-A180-955CEE5697F5}" name="N" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{1B7691C3-923C-4E01-92E9-BAD16478DB72}" name="Copy q" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{DE5D2A1C-D75F-491A-98D0-A233B66BB08C}" name="Compare q" dataDxfId="5"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5607FA58-C544-441A-8987-5BE2B0F172ED}" name="Таблица73672" displayName="Таблица73672" ref="F2:H53" totalsRowShown="0">
+  <autoFilter ref="F2:H53" xr:uid="{5607FA58-C544-441A-8987-5BE2B0F172ED}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{ACEAB66B-AE32-45A2-8926-84E6302C5E34}" name="N"/>
+    <tableColumn id="2" xr3:uid="{11DAFB21-07B3-48E3-908A-5CFC4A1D1B33}" name="Copy sh" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{53077772-C28F-4257-85A8-0AB505F9C552}" name="Compare sh"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{79971A81-4FD2-4594-8052-CC4F7D0125A7}" name="Таблица73" displayName="Таблица73" ref="B2:D52" totalsRowShown="0" tableBorderDxfId="3">
+  <autoFilter ref="B2:D52" xr:uid="{79971A81-4FD2-4594-8052-CC4F7D0125A7}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{FEE85231-2D90-4F77-A4C5-25EA4911F4D0}" name="N" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{A2D10756-2042-4755-9BE2-14696913FBBE}" name="Copy q" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{24984630-59D9-464B-AB12-390715BE809E}" name="Compare q" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6360,4 +9890,1540 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2AC8A97-DDBA-4DB0-949A-D7A6A2EC5799}">
+  <dimension ref="B1:L53"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="F1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="J1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+    </row>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B3" s="5">
+        <v>1000</v>
+      </c>
+      <c r="C3" s="7">
+        <v>1998</v>
+      </c>
+      <c r="D3" s="6">
+        <v>999</v>
+      </c>
+      <c r="F3">
+        <v>1000</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>500500</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1000</v>
+      </c>
+      <c r="K3" s="7">
+        <v>1998</v>
+      </c>
+      <c r="L3" s="6">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="5">
+        <v>2000</v>
+      </c>
+      <c r="C4" s="7">
+        <v>3998</v>
+      </c>
+      <c r="D4" s="6">
+        <v>1999</v>
+      </c>
+      <c r="F4">
+        <v>2000</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>2001000</v>
+      </c>
+      <c r="J4" s="5">
+        <v>2000</v>
+      </c>
+      <c r="K4" s="7">
+        <v>3998</v>
+      </c>
+      <c r="L4" s="6">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B5" s="5">
+        <v>3000</v>
+      </c>
+      <c r="C5" s="7">
+        <v>5998</v>
+      </c>
+      <c r="D5" s="6">
+        <v>2999</v>
+      </c>
+      <c r="F5">
+        <v>3000</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>4501500</v>
+      </c>
+      <c r="J5" s="5">
+        <v>3000</v>
+      </c>
+      <c r="K5" s="7">
+        <v>5998</v>
+      </c>
+      <c r="L5" s="6">
+        <v>2999</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B6" s="5">
+        <v>4000</v>
+      </c>
+      <c r="C6" s="7">
+        <v>7998</v>
+      </c>
+      <c r="D6" s="6">
+        <v>3999</v>
+      </c>
+      <c r="F6">
+        <v>4000</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>8002000</v>
+      </c>
+      <c r="J6" s="5">
+        <v>4000</v>
+      </c>
+      <c r="K6">
+        <v>7998</v>
+      </c>
+      <c r="L6">
+        <v>3999</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B7" s="5">
+        <v>5000</v>
+      </c>
+      <c r="C7" s="7">
+        <v>9998</v>
+      </c>
+      <c r="D7" s="6">
+        <v>4999</v>
+      </c>
+      <c r="F7">
+        <v>5000</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>12502500</v>
+      </c>
+      <c r="J7" s="5">
+        <v>5000</v>
+      </c>
+      <c r="K7">
+        <v>9998</v>
+      </c>
+      <c r="L7">
+        <v>4999</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B8" s="5">
+        <v>6000</v>
+      </c>
+      <c r="C8" s="7">
+        <v>11998</v>
+      </c>
+      <c r="D8" s="6">
+        <v>5999</v>
+      </c>
+      <c r="F8">
+        <v>6000</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>18003000</v>
+      </c>
+      <c r="J8" s="5">
+        <v>6000</v>
+      </c>
+      <c r="K8">
+        <v>11998</v>
+      </c>
+      <c r="L8">
+        <v>5999</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B9" s="5">
+        <v>7000</v>
+      </c>
+      <c r="C9" s="7">
+        <v>13998</v>
+      </c>
+      <c r="D9" s="6">
+        <v>6999</v>
+      </c>
+      <c r="F9">
+        <v>7000</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>24503500</v>
+      </c>
+      <c r="J9" s="5">
+        <v>7000</v>
+      </c>
+      <c r="K9">
+        <v>13998</v>
+      </c>
+      <c r="L9">
+        <v>6999</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B10" s="5">
+        <v>8000</v>
+      </c>
+      <c r="C10" s="7">
+        <v>15998</v>
+      </c>
+      <c r="D10" s="6">
+        <v>7999</v>
+      </c>
+      <c r="F10">
+        <v>8000</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>32004000</v>
+      </c>
+      <c r="J10" s="5">
+        <v>8000</v>
+      </c>
+      <c r="K10">
+        <v>15998</v>
+      </c>
+      <c r="L10">
+        <v>7999</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B11" s="5">
+        <v>9000</v>
+      </c>
+      <c r="C11" s="7">
+        <v>17998</v>
+      </c>
+      <c r="D11" s="6">
+        <v>8999</v>
+      </c>
+      <c r="F11">
+        <v>9000</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>40504500</v>
+      </c>
+      <c r="J11" s="5">
+        <v>9000</v>
+      </c>
+      <c r="K11">
+        <v>17998</v>
+      </c>
+      <c r="L11">
+        <v>8999</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B12" s="5">
+        <v>10000</v>
+      </c>
+      <c r="C12" s="7">
+        <v>19998</v>
+      </c>
+      <c r="D12" s="6">
+        <v>9999</v>
+      </c>
+      <c r="F12">
+        <v>10000</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>50005000</v>
+      </c>
+      <c r="J12" s="5">
+        <v>10000</v>
+      </c>
+      <c r="K12">
+        <v>19998</v>
+      </c>
+      <c r="L12">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B13" s="5">
+        <v>11000</v>
+      </c>
+      <c r="C13" s="7">
+        <v>21998</v>
+      </c>
+      <c r="D13" s="6">
+        <v>10999</v>
+      </c>
+      <c r="F13">
+        <v>11000</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>60505500</v>
+      </c>
+      <c r="J13" s="5">
+        <v>11000</v>
+      </c>
+      <c r="K13">
+        <v>21998</v>
+      </c>
+      <c r="L13">
+        <v>10999</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B14" s="5">
+        <v>12000</v>
+      </c>
+      <c r="C14" s="7">
+        <v>23998</v>
+      </c>
+      <c r="D14" s="6">
+        <v>11999</v>
+      </c>
+      <c r="F14">
+        <v>12000</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>72006000</v>
+      </c>
+      <c r="J14" s="5">
+        <v>12000</v>
+      </c>
+      <c r="K14">
+        <v>23998</v>
+      </c>
+      <c r="L14">
+        <v>11999</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B15" s="5">
+        <v>13000</v>
+      </c>
+      <c r="C15" s="7">
+        <v>25998</v>
+      </c>
+      <c r="D15" s="6">
+        <v>12999</v>
+      </c>
+      <c r="F15">
+        <v>13000</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>84506500</v>
+      </c>
+      <c r="J15" s="5">
+        <v>13000</v>
+      </c>
+      <c r="K15">
+        <v>25998</v>
+      </c>
+      <c r="L15">
+        <v>12999</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B16" s="5">
+        <v>14000</v>
+      </c>
+      <c r="C16" s="7">
+        <v>27998</v>
+      </c>
+      <c r="D16" s="6">
+        <v>13999</v>
+      </c>
+      <c r="F16">
+        <v>14000</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>98007000</v>
+      </c>
+      <c r="J16" s="5">
+        <v>14000</v>
+      </c>
+      <c r="K16">
+        <v>27998</v>
+      </c>
+      <c r="L16">
+        <v>13999</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B17" s="5">
+        <v>15000</v>
+      </c>
+      <c r="C17" s="7">
+        <v>29998</v>
+      </c>
+      <c r="D17" s="6">
+        <v>14999</v>
+      </c>
+      <c r="F17">
+        <v>15000</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>112507500</v>
+      </c>
+      <c r="J17" s="5">
+        <v>15000</v>
+      </c>
+      <c r="K17">
+        <v>29998</v>
+      </c>
+      <c r="L17">
+        <v>14999</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B18" s="5">
+        <v>16000</v>
+      </c>
+      <c r="C18" s="7">
+        <v>31998</v>
+      </c>
+      <c r="D18" s="6">
+        <v>15999</v>
+      </c>
+      <c r="F18">
+        <v>16000</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>128008000</v>
+      </c>
+      <c r="J18" s="5">
+        <v>16000</v>
+      </c>
+      <c r="K18">
+        <v>31998</v>
+      </c>
+      <c r="L18">
+        <v>15999</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B19" s="5">
+        <v>17000</v>
+      </c>
+      <c r="C19" s="7">
+        <v>33998</v>
+      </c>
+      <c r="D19" s="6">
+        <v>16999</v>
+      </c>
+      <c r="F19">
+        <v>17000</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>144508500</v>
+      </c>
+      <c r="J19" s="5">
+        <v>17000</v>
+      </c>
+      <c r="K19">
+        <v>33998</v>
+      </c>
+      <c r="L19">
+        <v>16999</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B20" s="5">
+        <v>18000</v>
+      </c>
+      <c r="C20" s="7">
+        <v>35998</v>
+      </c>
+      <c r="D20" s="6">
+        <v>17999</v>
+      </c>
+      <c r="F20">
+        <v>18000</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>162009000</v>
+      </c>
+      <c r="J20" s="5">
+        <v>18000</v>
+      </c>
+      <c r="K20">
+        <v>35998</v>
+      </c>
+      <c r="L20">
+        <v>17999</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B21" s="5">
+        <v>19000</v>
+      </c>
+      <c r="C21" s="7">
+        <v>37998</v>
+      </c>
+      <c r="D21" s="6">
+        <v>18999</v>
+      </c>
+      <c r="F21">
+        <v>19000</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>180509500</v>
+      </c>
+      <c r="J21" s="5">
+        <v>19000</v>
+      </c>
+      <c r="K21">
+        <v>37998</v>
+      </c>
+      <c r="L21">
+        <v>18999</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B22" s="5">
+        <v>20000</v>
+      </c>
+      <c r="C22" s="7">
+        <v>39998</v>
+      </c>
+      <c r="D22" s="6">
+        <v>19999</v>
+      </c>
+      <c r="F22">
+        <v>20000</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>200010000</v>
+      </c>
+      <c r="J22" s="5">
+        <v>20000</v>
+      </c>
+      <c r="K22">
+        <v>39998</v>
+      </c>
+      <c r="L22">
+        <v>19999</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B23" s="5">
+        <v>21000</v>
+      </c>
+      <c r="C23" s="7">
+        <v>41998</v>
+      </c>
+      <c r="D23" s="6">
+        <v>20999</v>
+      </c>
+      <c r="F23">
+        <v>21000</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>220510500</v>
+      </c>
+      <c r="J23" s="5">
+        <v>21000</v>
+      </c>
+      <c r="K23">
+        <v>41998</v>
+      </c>
+      <c r="L23">
+        <v>20999</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B24" s="5">
+        <v>22000</v>
+      </c>
+      <c r="C24" s="7">
+        <v>43998</v>
+      </c>
+      <c r="D24" s="6">
+        <v>21999</v>
+      </c>
+      <c r="F24">
+        <v>22000</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>242011000</v>
+      </c>
+      <c r="J24" s="5">
+        <v>22000</v>
+      </c>
+      <c r="K24">
+        <v>43998</v>
+      </c>
+      <c r="L24">
+        <v>21999</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B25" s="5">
+        <v>23000</v>
+      </c>
+      <c r="C25" s="7">
+        <v>45998</v>
+      </c>
+      <c r="D25" s="6">
+        <v>22999</v>
+      </c>
+      <c r="F25">
+        <v>23000</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>264511500</v>
+      </c>
+      <c r="J25" s="5">
+        <v>23000</v>
+      </c>
+      <c r="K25">
+        <v>45998</v>
+      </c>
+      <c r="L25">
+        <v>22999</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B26" s="5">
+        <v>24000</v>
+      </c>
+      <c r="C26" s="7">
+        <v>47998</v>
+      </c>
+      <c r="D26" s="6">
+        <v>23999</v>
+      </c>
+      <c r="F26">
+        <v>24000</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>288012000</v>
+      </c>
+      <c r="J26" s="5">
+        <v>24000</v>
+      </c>
+      <c r="K26">
+        <v>47998</v>
+      </c>
+      <c r="L26">
+        <v>23999</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B27" s="5">
+        <v>25000</v>
+      </c>
+      <c r="C27" s="7">
+        <v>49998</v>
+      </c>
+      <c r="D27" s="6">
+        <v>24999</v>
+      </c>
+      <c r="F27">
+        <v>25000</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>312512500</v>
+      </c>
+      <c r="J27" s="5">
+        <v>25000</v>
+      </c>
+      <c r="K27">
+        <v>49998</v>
+      </c>
+      <c r="L27">
+        <v>24999</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B28" s="5">
+        <v>26000</v>
+      </c>
+      <c r="C28" s="7">
+        <v>51998</v>
+      </c>
+      <c r="D28" s="6">
+        <v>25999</v>
+      </c>
+      <c r="F28">
+        <v>26000</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>338013000</v>
+      </c>
+      <c r="J28" s="5">
+        <v>26000</v>
+      </c>
+      <c r="K28">
+        <v>51998</v>
+      </c>
+      <c r="L28">
+        <v>25999</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B29" s="5">
+        <v>27000</v>
+      </c>
+      <c r="C29" s="7">
+        <v>53998</v>
+      </c>
+      <c r="D29" s="6">
+        <v>26999</v>
+      </c>
+      <c r="F29">
+        <v>27000</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>364513500</v>
+      </c>
+      <c r="J29" s="5">
+        <v>27000</v>
+      </c>
+      <c r="K29">
+        <v>53998</v>
+      </c>
+      <c r="L29">
+        <v>26999</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B30" s="5">
+        <v>28000</v>
+      </c>
+      <c r="C30" s="7">
+        <v>55998</v>
+      </c>
+      <c r="D30" s="6">
+        <v>27999</v>
+      </c>
+      <c r="F30">
+        <v>28000</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>392014000</v>
+      </c>
+      <c r="J30" s="5">
+        <v>28000</v>
+      </c>
+      <c r="K30">
+        <v>55998</v>
+      </c>
+      <c r="L30">
+        <v>27999</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B31" s="5">
+        <v>29000</v>
+      </c>
+      <c r="C31" s="7">
+        <v>57998</v>
+      </c>
+      <c r="D31" s="6">
+        <v>28999</v>
+      </c>
+      <c r="F31">
+        <v>29000</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>420514500</v>
+      </c>
+      <c r="J31" s="5">
+        <v>29000</v>
+      </c>
+      <c r="K31">
+        <v>57998</v>
+      </c>
+      <c r="L31">
+        <v>28999</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B32" s="5">
+        <v>30000</v>
+      </c>
+      <c r="C32" s="7">
+        <v>59998</v>
+      </c>
+      <c r="D32" s="6">
+        <v>29999</v>
+      </c>
+      <c r="F32">
+        <v>30000</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>450015000</v>
+      </c>
+      <c r="J32" s="5">
+        <v>30000</v>
+      </c>
+      <c r="K32">
+        <v>59998</v>
+      </c>
+      <c r="L32">
+        <v>29999</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B33" s="5">
+        <v>31000</v>
+      </c>
+      <c r="C33" s="7">
+        <v>61998</v>
+      </c>
+      <c r="D33" s="6">
+        <v>30999</v>
+      </c>
+      <c r="F33">
+        <v>31000</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>480515500</v>
+      </c>
+      <c r="J33" s="5">
+        <v>31000</v>
+      </c>
+      <c r="K33">
+        <v>61998</v>
+      </c>
+      <c r="L33">
+        <v>30999</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B34" s="5">
+        <v>32000</v>
+      </c>
+      <c r="C34" s="7">
+        <v>63998</v>
+      </c>
+      <c r="D34" s="6">
+        <v>31999</v>
+      </c>
+      <c r="F34">
+        <v>32000</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>512016000</v>
+      </c>
+      <c r="J34" s="5">
+        <v>32000</v>
+      </c>
+      <c r="K34">
+        <v>63998</v>
+      </c>
+      <c r="L34">
+        <v>31999</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B35" s="5">
+        <v>33000</v>
+      </c>
+      <c r="C35" s="7">
+        <v>65998</v>
+      </c>
+      <c r="D35" s="6">
+        <v>32999</v>
+      </c>
+      <c r="F35">
+        <v>33000</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>544516500</v>
+      </c>
+      <c r="J35" s="5">
+        <v>33000</v>
+      </c>
+      <c r="K35">
+        <v>65998</v>
+      </c>
+      <c r="L35">
+        <v>32999</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B36" s="5">
+        <v>34000</v>
+      </c>
+      <c r="C36" s="7">
+        <v>67998</v>
+      </c>
+      <c r="D36" s="6">
+        <v>33999</v>
+      </c>
+      <c r="F36">
+        <v>34000</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>578017000</v>
+      </c>
+      <c r="J36" s="5">
+        <v>34000</v>
+      </c>
+      <c r="K36">
+        <v>67998</v>
+      </c>
+      <c r="L36">
+        <v>33999</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B37" s="5">
+        <v>35000</v>
+      </c>
+      <c r="C37" s="7">
+        <v>69998</v>
+      </c>
+      <c r="D37" s="6">
+        <v>34999</v>
+      </c>
+      <c r="F37">
+        <v>35000</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>612517500</v>
+      </c>
+      <c r="J37" s="5">
+        <v>35000</v>
+      </c>
+      <c r="K37">
+        <v>69998</v>
+      </c>
+      <c r="L37">
+        <v>34999</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B38" s="5">
+        <v>36000</v>
+      </c>
+      <c r="C38" s="7">
+        <v>71998</v>
+      </c>
+      <c r="D38" s="6">
+        <v>35999</v>
+      </c>
+      <c r="F38">
+        <v>36000</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>648018000</v>
+      </c>
+      <c r="J38" s="5">
+        <v>36000</v>
+      </c>
+      <c r="K38">
+        <v>71998</v>
+      </c>
+      <c r="L38">
+        <v>35999</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B39" s="5">
+        <v>37000</v>
+      </c>
+      <c r="C39" s="7">
+        <v>73998</v>
+      </c>
+      <c r="D39" s="6">
+        <v>36999</v>
+      </c>
+      <c r="F39">
+        <v>37000</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>684518500</v>
+      </c>
+      <c r="J39" s="5">
+        <v>37000</v>
+      </c>
+      <c r="K39">
+        <v>73998</v>
+      </c>
+      <c r="L39">
+        <v>36999</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B40" s="5">
+        <v>38000</v>
+      </c>
+      <c r="C40" s="7">
+        <v>75998</v>
+      </c>
+      <c r="D40" s="6">
+        <v>37999</v>
+      </c>
+      <c r="F40">
+        <v>38000</v>
+      </c>
+      <c r="G40" s="1">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>722019000</v>
+      </c>
+      <c r="J40" s="5">
+        <v>38000</v>
+      </c>
+      <c r="K40">
+        <v>75998</v>
+      </c>
+      <c r="L40">
+        <v>37999</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B41" s="5">
+        <v>39000</v>
+      </c>
+      <c r="C41" s="7">
+        <v>77998</v>
+      </c>
+      <c r="D41" s="6">
+        <v>38999</v>
+      </c>
+      <c r="F41">
+        <v>39000</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>760519500</v>
+      </c>
+      <c r="J41" s="5">
+        <v>39000</v>
+      </c>
+      <c r="K41">
+        <v>77998</v>
+      </c>
+      <c r="L41">
+        <v>38999</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B42" s="5">
+        <v>40000</v>
+      </c>
+      <c r="C42" s="7">
+        <v>79998</v>
+      </c>
+      <c r="D42" s="6">
+        <v>39999</v>
+      </c>
+      <c r="F42">
+        <v>40000</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>800020000</v>
+      </c>
+      <c r="J42" s="5">
+        <v>40000</v>
+      </c>
+      <c r="K42">
+        <v>79998</v>
+      </c>
+      <c r="L42">
+        <v>39999</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B43" s="5">
+        <v>41000</v>
+      </c>
+      <c r="C43" s="7">
+        <v>81998</v>
+      </c>
+      <c r="D43" s="6">
+        <v>40999</v>
+      </c>
+      <c r="F43">
+        <v>41000</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>840520500</v>
+      </c>
+      <c r="J43" s="5">
+        <v>41000</v>
+      </c>
+      <c r="K43">
+        <v>81998</v>
+      </c>
+      <c r="L43">
+        <v>40999</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B44" s="5">
+        <v>42000</v>
+      </c>
+      <c r="C44" s="7">
+        <v>83998</v>
+      </c>
+      <c r="D44" s="6">
+        <v>41999</v>
+      </c>
+      <c r="F44">
+        <v>42000</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>882021000</v>
+      </c>
+      <c r="J44" s="5">
+        <v>42000</v>
+      </c>
+      <c r="K44">
+        <v>83998</v>
+      </c>
+      <c r="L44">
+        <v>41999</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B45" s="5">
+        <v>43000</v>
+      </c>
+      <c r="C45" s="7">
+        <v>85998</v>
+      </c>
+      <c r="D45" s="6">
+        <v>42999</v>
+      </c>
+      <c r="F45">
+        <v>43000</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>924521500</v>
+      </c>
+      <c r="J45" s="5">
+        <v>43000</v>
+      </c>
+      <c r="K45">
+        <v>85998</v>
+      </c>
+      <c r="L45">
+        <v>42999</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B46" s="5">
+        <v>44000</v>
+      </c>
+      <c r="C46" s="7">
+        <v>87998</v>
+      </c>
+      <c r="D46" s="6">
+        <v>43999</v>
+      </c>
+      <c r="F46">
+        <v>44000</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>968022000</v>
+      </c>
+      <c r="J46" s="5">
+        <v>44000</v>
+      </c>
+      <c r="K46">
+        <v>87998</v>
+      </c>
+      <c r="L46">
+        <v>43999</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B47" s="5">
+        <v>45000</v>
+      </c>
+      <c r="C47" s="7">
+        <v>89998</v>
+      </c>
+      <c r="D47" s="6">
+        <v>44999</v>
+      </c>
+      <c r="F47">
+        <v>45000</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>1012522500</v>
+      </c>
+      <c r="J47" s="5">
+        <v>45000</v>
+      </c>
+      <c r="K47">
+        <v>89998</v>
+      </c>
+      <c r="L47">
+        <v>44999</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B48" s="5">
+        <v>46000</v>
+      </c>
+      <c r="C48" s="7">
+        <v>91998</v>
+      </c>
+      <c r="D48" s="6">
+        <v>45999</v>
+      </c>
+      <c r="F48">
+        <v>46000</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>1058023000</v>
+      </c>
+      <c r="J48" s="5">
+        <v>46000</v>
+      </c>
+      <c r="K48">
+        <v>91998</v>
+      </c>
+      <c r="L48">
+        <v>45999</v>
+      </c>
+    </row>
+    <row r="49" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B49" s="5">
+        <v>47000</v>
+      </c>
+      <c r="C49" s="7">
+        <v>93998</v>
+      </c>
+      <c r="D49" s="6">
+        <v>46999</v>
+      </c>
+      <c r="F49">
+        <v>47000</v>
+      </c>
+      <c r="G49" s="1">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>1104523500</v>
+      </c>
+      <c r="J49" s="5">
+        <v>47000</v>
+      </c>
+      <c r="K49">
+        <v>93998</v>
+      </c>
+      <c r="L49">
+        <v>46999</v>
+      </c>
+    </row>
+    <row r="50" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B50" s="5">
+        <v>48000</v>
+      </c>
+      <c r="C50" s="7">
+        <v>95998</v>
+      </c>
+      <c r="D50" s="6">
+        <v>47999</v>
+      </c>
+      <c r="F50">
+        <v>48000</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>1152024000</v>
+      </c>
+      <c r="J50" s="5">
+        <v>48000</v>
+      </c>
+      <c r="K50">
+        <v>95998</v>
+      </c>
+      <c r="L50">
+        <v>47999</v>
+      </c>
+    </row>
+    <row r="51" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B51" s="5">
+        <v>49000</v>
+      </c>
+      <c r="C51" s="7">
+        <v>97998</v>
+      </c>
+      <c r="D51" s="6">
+        <v>48999</v>
+      </c>
+      <c r="F51">
+        <v>49000</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>1200524500</v>
+      </c>
+      <c r="J51" s="5">
+        <v>49000</v>
+      </c>
+      <c r="K51">
+        <v>97998</v>
+      </c>
+      <c r="L51">
+        <v>48999</v>
+      </c>
+    </row>
+    <row r="52" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B52" s="5">
+        <v>50000</v>
+      </c>
+      <c r="C52" s="7">
+        <v>99998</v>
+      </c>
+      <c r="D52" s="6">
+        <v>49999</v>
+      </c>
+      <c r="F52">
+        <v>50000</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>1250025000</v>
+      </c>
+      <c r="J52" s="5">
+        <v>50000</v>
+      </c>
+      <c r="K52">
+        <v>99998</v>
+      </c>
+      <c r="L52">
+        <v>4999</v>
+      </c>
+    </row>
+    <row r="53" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="G53" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="J1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="2">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7F3347C-990F-4F42-BAAC-9CF0059C811E}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/exp2.xlsx
+++ b/exp2.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\3sem_git\Algs_and_data_structures\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Algs_and_data_structures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0803815E-F8D7-4123-BA6B-6DB05F0EFC8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD5D19A8-316B-440B-9F2C-1D21839DDA5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="random" sheetId="1" r:id="rId1"/>
     <sheet name="r_gr" sheetId="4" r:id="rId2"/>
     <sheet name="sorted" sheetId="5" r:id="rId3"/>
     <sheet name="s_gr" sheetId="6" r:id="rId4"/>
+    <sheet name="reverse_sorted" sheetId="7" r:id="rId5"/>
+    <sheet name="rs_gr" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="10">
   <si>
     <t>N</t>
   </si>
@@ -154,7 +156,106 @@
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="15">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3106,7 +3207,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="FFC000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -3457,7 +3558,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:schemeClr val="accent6"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -3808,7 +3909,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent3"/>
+                <a:srgbClr val="0070C0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -4430,7 +4531,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="FFC000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -4781,7 +4882,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:schemeClr val="accent6"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -5132,7 +5233,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent3"/>
+                <a:srgbClr val="0070C0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -5582,6 +5683,2655 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="545023183"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FFC000"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>COPY</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>reverse_sorted!$C$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Copy q</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>reverse_sorted!$B$3:$B$52</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17000</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18000</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19000</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20000</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21000</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22000</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23000</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24000</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25000</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26000</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27000</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28000</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29000</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30000</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>31000</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>32000</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33000</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34000</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35000</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36000</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37000</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>38000</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>39000</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>40000</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>41000</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>42000</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>43000</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>44000</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45000</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46000</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>47000</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>48000</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>49000</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>50000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>reverse_sorted!$C$3:$C$52</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>2499</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7499</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12499</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>14999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>17499</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>19999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>22499</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>27499</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>29999</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>32499</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>34999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>37499</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>39999</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>42499</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>44999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>47499</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>49999</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>52499</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>54999</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>57499</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>59999</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>62499</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>64999</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>67499</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>69999</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>72499</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>74999</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>77499</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>79999</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>82499</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>84999</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>87499</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>89999</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>92499</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>94999</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>97499</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>99999</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>102499</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>104999</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>107499</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>109999</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>112499</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>114999</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>117499</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>119999</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>122499</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>124999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1DA1-4FC1-A12E-CFC2AB433A6A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>reverse_sorted!$G$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Copy sh</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>reverse_sorted!$B$3:$B$52</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17000</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18000</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19000</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20000</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21000</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22000</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23000</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24000</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25000</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26000</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27000</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28000</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29000</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30000</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>31000</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>32000</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33000</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34000</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35000</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36000</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37000</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>38000</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>39000</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>40000</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>41000</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>42000</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>43000</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>44000</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45000</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46000</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>47000</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>48000</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>49000</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>50000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>reverse_sorted!$G$3:$G$52</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>1498500</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5997000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>13495500</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>23994000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>37492500</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>53991000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>73489500</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>95988000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>121486500</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>149985000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>181483500</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>215982000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>253480500</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>293979000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>337477500</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>383976000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>433474500</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>485973000</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>541471500</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>599970000</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>661468500</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>725967000</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>793465500</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>863964000</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>937462500</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1013961000</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1093459500</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1175958000</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1261456500</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1349955000</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1441453500</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1535952000</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1633450500</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1733949000</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1837447500</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1943946000</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2053444500</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2165943000</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2281441500</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2399940000</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2521438500</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2645937000</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2773435500</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2903934000</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>3037432500</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>3173931000</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>3313429500</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>3455928000</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>3601426500</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>3749925000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1DA1-4FC1-A12E-CFC2AB433A6A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>reverse_sorted!$K$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Copy ins</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>reverse_sorted!$B$3:$B$52</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17000</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18000</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19000</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20000</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21000</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22000</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23000</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24000</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25000</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26000</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27000</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28000</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29000</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30000</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>31000</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>32000</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33000</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34000</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35000</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36000</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37000</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>38000</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>39000</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>40000</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>41000</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>42000</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>43000</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>44000</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45000</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46000</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>47000</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>48000</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>49000</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>50000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>reverse_sorted!$K$3:$K$52</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>501498</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2002998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4504498</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="General">
+                  <c:v>8005998</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="General">
+                  <c:v>12507498</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="General">
+                  <c:v>18008998</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="General">
+                  <c:v>24510498</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="General">
+                  <c:v>32011998</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="General">
+                  <c:v>40513498</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="General">
+                  <c:v>50014998</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="General">
+                  <c:v>60516498</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="General">
+                  <c:v>72017998</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="General">
+                  <c:v>84519498</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="General">
+                  <c:v>98020998</c:v>
+                </c:pt>
+                <c:pt idx="14" formatCode="General">
+                  <c:v>112522498</c:v>
+                </c:pt>
+                <c:pt idx="15" formatCode="General">
+                  <c:v>128023998</c:v>
+                </c:pt>
+                <c:pt idx="16" formatCode="General">
+                  <c:v>144525498</c:v>
+                </c:pt>
+                <c:pt idx="17" formatCode="General">
+                  <c:v>162026998</c:v>
+                </c:pt>
+                <c:pt idx="18" formatCode="General">
+                  <c:v>180528498</c:v>
+                </c:pt>
+                <c:pt idx="19" formatCode="General">
+                  <c:v>200029998</c:v>
+                </c:pt>
+                <c:pt idx="20" formatCode="General">
+                  <c:v>220531498</c:v>
+                </c:pt>
+                <c:pt idx="21" formatCode="General">
+                  <c:v>242032998</c:v>
+                </c:pt>
+                <c:pt idx="22" formatCode="General">
+                  <c:v>264534498</c:v>
+                </c:pt>
+                <c:pt idx="23" formatCode="General">
+                  <c:v>288035998</c:v>
+                </c:pt>
+                <c:pt idx="24" formatCode="General">
+                  <c:v>312537498</c:v>
+                </c:pt>
+                <c:pt idx="25" formatCode="General">
+                  <c:v>338038998</c:v>
+                </c:pt>
+                <c:pt idx="26" formatCode="General">
+                  <c:v>364540498</c:v>
+                </c:pt>
+                <c:pt idx="27" formatCode="General">
+                  <c:v>392041998</c:v>
+                </c:pt>
+                <c:pt idx="28" formatCode="General">
+                  <c:v>420543498</c:v>
+                </c:pt>
+                <c:pt idx="29" formatCode="General">
+                  <c:v>450044998</c:v>
+                </c:pt>
+                <c:pt idx="30" formatCode="General">
+                  <c:v>480546498</c:v>
+                </c:pt>
+                <c:pt idx="31" formatCode="General">
+                  <c:v>512047998</c:v>
+                </c:pt>
+                <c:pt idx="32" formatCode="General">
+                  <c:v>544549498</c:v>
+                </c:pt>
+                <c:pt idx="33" formatCode="General">
+                  <c:v>578050998</c:v>
+                </c:pt>
+                <c:pt idx="34" formatCode="General">
+                  <c:v>612552498</c:v>
+                </c:pt>
+                <c:pt idx="35" formatCode="General">
+                  <c:v>648053998</c:v>
+                </c:pt>
+                <c:pt idx="36" formatCode="General">
+                  <c:v>684555498</c:v>
+                </c:pt>
+                <c:pt idx="37" formatCode="General">
+                  <c:v>722056998</c:v>
+                </c:pt>
+                <c:pt idx="38" formatCode="General">
+                  <c:v>760558498</c:v>
+                </c:pt>
+                <c:pt idx="39" formatCode="General">
+                  <c:v>800059998</c:v>
+                </c:pt>
+                <c:pt idx="40" formatCode="General">
+                  <c:v>840561498</c:v>
+                </c:pt>
+                <c:pt idx="41" formatCode="General">
+                  <c:v>882062998</c:v>
+                </c:pt>
+                <c:pt idx="42" formatCode="General">
+                  <c:v>924564498</c:v>
+                </c:pt>
+                <c:pt idx="43" formatCode="General">
+                  <c:v>968065998</c:v>
+                </c:pt>
+                <c:pt idx="44" formatCode="General">
+                  <c:v>1012567498</c:v>
+                </c:pt>
+                <c:pt idx="45" formatCode="General">
+                  <c:v>1058068998</c:v>
+                </c:pt>
+                <c:pt idx="46" formatCode="General">
+                  <c:v>1104570498</c:v>
+                </c:pt>
+                <c:pt idx="47" formatCode="General">
+                  <c:v>1152071998</c:v>
+                </c:pt>
+                <c:pt idx="48" formatCode="General">
+                  <c:v>1200573498</c:v>
+                </c:pt>
+                <c:pt idx="49" formatCode="General">
+                  <c:v>1250074998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-1DA1-4FC1-A12E-CFC2AB433A6A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="602377272"/>
+        <c:axId val="602375472"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="602377272"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="602375472"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="602375472"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="602377272"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>COMPARE</a:t>
+            </a:r>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>reverse_sorted!$D$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Compare q</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>reverse_sorted!$B$3:$B$52</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17000</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18000</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19000</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20000</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21000</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22000</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23000</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24000</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25000</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26000</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27000</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28000</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29000</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30000</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>31000</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>32000</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33000</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34000</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35000</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36000</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37000</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>38000</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>39000</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>40000</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>41000</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>42000</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>43000</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>44000</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45000</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46000</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>47000</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>48000</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>49000</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>50000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>reverse_sorted!$D$3:$D$52</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>12973</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>27949</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>43901</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>59901</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>76805</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>93805</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>110805</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>127805</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>145613</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>163613</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>181613</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>199613</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>217613</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>235613</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>253613</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>271613</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>290229</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>309229</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>328229</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>347229</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>366229</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>385229</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>404229</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>423229</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>442229</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>461229</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>480229</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>499229</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>518229</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>537229</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>556229</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>575229</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>594461</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>614461</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>634461</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>654461</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>674461</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>694461</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>714461</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>734461</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>754461</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>774461</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>794461</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>814461</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>834461</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>854461</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>874461</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>894461</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>914461</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>934461</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-CA5A-4529-BA60-5A95F494F94B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>reverse_sorted!$H$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Compare sh</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>reverse_sorted!$B$3:$B$52</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17000</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18000</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19000</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20000</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21000</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22000</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23000</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24000</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25000</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26000</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27000</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28000</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29000</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30000</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>31000</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>32000</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33000</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34000</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35000</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36000</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37000</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>38000</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>39000</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>40000</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>41000</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>42000</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>43000</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>44000</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45000</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46000</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>47000</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>48000</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>49000</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>50000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>reverse_sorted!$H$3:$H$52</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>500500</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2001000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4501500</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8002000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12502500</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>18003000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>24503500</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>32004000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>40504500</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>50005000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>60505500</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>72006000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>84506500</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>98007000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>112507500</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>128008000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>144508500</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>162009000</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>180509500</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>200010000</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>220510500</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>242011000</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>264511500</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>288012000</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>312512500</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>338013000</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>364513500</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>392014000</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>420514500</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>450015000</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>480515500</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>512016000</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>544516500</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>578017000</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>612517500</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>648018000</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>684518500</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>722019000</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>760519500</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>800020000</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>840520500</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>882021000</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>924521500</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>968022000</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1012522500</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1058023000</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1104523500</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1152024000</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1200524500</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1250025000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-CA5A-4529-BA60-5A95F494F94B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>reverse_sorted!$L$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Compare ins</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>reverse_sorted!$B$3:$B$52</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17000</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18000</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19000</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20000</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21000</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22000</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23000</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24000</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25000</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26000</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27000</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28000</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29000</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30000</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>31000</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>32000</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33000</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34000</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35000</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36000</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37000</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>38000</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>39000</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>40000</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>41000</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>42000</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>43000</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>44000</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45000</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46000</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>47000</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>48000</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>49000</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>50000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>reverse_sorted!$L$3:$L$52</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>500499</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2000999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4501499</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8001999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12502499</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>18002999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>24503499</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>32003999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>40504499</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>50004999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>60505499</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>72005999</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>84506499</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>98006999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>112507499</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>128007999</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>144508499</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>162008999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>180509499</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>200009999</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>220510499</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>242010999</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>264511499</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>288011999</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>312512499</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>338012999</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>364513499</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>392013999</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>420514499</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>450014999</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>480515499</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>512015999</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>544516499</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>578016999</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>612517499</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>648017999</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>684518499</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>722018999</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>760519499</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>800019999</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>840520499</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>882020999</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>924521499</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>968021999</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1012522499</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1058022999</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1104523499</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1152023999</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1200524499</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1250024999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-CA5A-4529-BA60-5A95F494F94B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="605273368"/>
+        <c:axId val="605270848"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="605273368"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="605270848"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="605270848"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="605273368"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5821,6 +8571,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
@@ -7370,6 +10200,1038 @@
 </file>
 
 <file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -8047,12 +11909,93 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>10026</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>170446</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Диаграмма 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44084FF5-22D4-4C5A-B327-3C2C122A2CBC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>30078</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>10025</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>205539</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>40104</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Диаграмма 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2164B8CD-E5E3-499A-BCFF-E68A221A1381}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{12DBA126-0BED-484C-AA50-D6AE7A611FC4}" name="Таблица7367" displayName="Таблица7367" ref="F2:H53" totalsRowShown="0">
   <autoFilter ref="F2:H53" xr:uid="{12DBA126-0BED-484C-AA50-D6AE7A611FC4}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{609707E7-BB94-42A5-917D-9570B5AC7EEF}" name="N"/>
-    <tableColumn id="2" xr3:uid="{65B1B6C8-8ACD-417E-A7A0-594CC47A6D37}" name="Copy sh" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{65B1B6C8-8ACD-417E-A7A0-594CC47A6D37}" name="Copy sh" dataDxfId="14"/>
     <tableColumn id="3" xr3:uid="{F893E8C0-37FA-4D96-8689-B68BE51E2DFE}" name="Compare sh"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -8060,12 +12003,12 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{3A419A4E-1F00-42E1-A1D0-7871938F171F}" name="Таблица7" displayName="Таблица7" ref="B2:D52" totalsRowShown="0" tableBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{3A419A4E-1F00-42E1-A1D0-7871938F171F}" name="Таблица7" displayName="Таблица7" ref="B2:D52" totalsRowShown="0" tableBorderDxfId="13">
   <autoFilter ref="B2:D52" xr:uid="{3A419A4E-1F00-42E1-A1D0-7871938F171F}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{C1BDC60F-4A13-494C-A180-955CEE5697F5}" name="N" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{1B7691C3-923C-4E01-92E9-BAD16478DB72}" name="Copy q" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{DE5D2A1C-D75F-491A-98D0-A233B66BB08C}" name="Compare q" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{C1BDC60F-4A13-494C-A180-955CEE5697F5}" name="N" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{1B7691C3-923C-4E01-92E9-BAD16478DB72}" name="Copy q" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{DE5D2A1C-D75F-491A-98D0-A233B66BB08C}" name="Compare q" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8076,7 +12019,7 @@
   <autoFilter ref="F2:H53" xr:uid="{5607FA58-C544-441A-8987-5BE2B0F172ED}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{ACEAB66B-AE32-45A2-8926-84E6302C5E34}" name="N"/>
-    <tableColumn id="2" xr3:uid="{11DAFB21-07B3-48E3-908A-5CFC4A1D1B33}" name="Copy sh" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{11DAFB21-07B3-48E3-908A-5CFC4A1D1B33}" name="Copy sh" dataDxfId="9"/>
     <tableColumn id="3" xr3:uid="{53077772-C28F-4257-85A8-0AB505F9C552}" name="Compare sh"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -8084,12 +12027,36 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{79971A81-4FD2-4594-8052-CC4F7D0125A7}" name="Таблица73" displayName="Таблица73" ref="B2:D52" totalsRowShown="0" tableBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{79971A81-4FD2-4594-8052-CC4F7D0125A7}" name="Таблица73" displayName="Таблица73" ref="B2:D52" totalsRowShown="0" tableBorderDxfId="8">
   <autoFilter ref="B2:D52" xr:uid="{79971A81-4FD2-4594-8052-CC4F7D0125A7}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{FEE85231-2D90-4F77-A4C5-25EA4911F4D0}" name="N" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{A2D10756-2042-4755-9BE2-14696913FBBE}" name="Copy q" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{24984630-59D9-464B-AB12-390715BE809E}" name="Compare q" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{FEE85231-2D90-4F77-A4C5-25EA4911F4D0}" name="N" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{A2D10756-2042-4755-9BE2-14696913FBBE}" name="Copy q" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{24984630-59D9-464B-AB12-390715BE809E}" name="Compare q" dataDxfId="5"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{ED744B51-A767-4A8E-B9D0-0D74B7E8AAE2}" name="Таблица73674" displayName="Таблица73674" ref="F2:H53" totalsRowShown="0">
+  <autoFilter ref="F2:H53" xr:uid="{ED744B51-A767-4A8E-B9D0-0D74B7E8AAE2}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{3F088BB7-E2AB-4740-8A11-CB8A7500598F}" name="N"/>
+    <tableColumn id="2" xr3:uid="{93D673C7-E911-4D6E-8346-FB7A0A7688F4}" name="Copy sh" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{3724D42B-91E7-4801-B2A7-9EB7767D914C}" name="Compare sh"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{19C91100-B377-4295-B55E-A294CE197BAF}" name="Таблица75" displayName="Таблица75" ref="B2:D52" totalsRowShown="0" tableBorderDxfId="3">
+  <autoFilter ref="B2:D52" xr:uid="{19C91100-B377-4295-B55E-A294CE197BAF}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{179A060F-CEF4-4233-842D-7560B1E84EA1}" name="N" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{C94038B0-6362-4C5E-BB84-74E87A8F8E1F}" name="Copy q" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{F5C1EFA1-AFAD-41AD-A8AD-009468CCF1F9}" name="Compare q" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8359,17 +12326,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:L53"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
@@ -8386,7 +12353,7 @@
       <c r="K1" s="8"/>
       <c r="L1" s="8"/>
     </row>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -8415,7 +12382,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="5">
         <v>1000</v>
       </c>
@@ -8444,7 +12411,7 @@
         <v>251381</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="5">
         <v>2000</v>
       </c>
@@ -8473,7 +12440,7 @@
         <v>960933</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="5">
         <v>3000</v>
       </c>
@@ -8502,7 +12469,7 @@
         <v>2218307</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="5">
         <v>4000</v>
       </c>
@@ -8531,7 +12498,7 @@
         <v>3989996</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
         <v>5000</v>
       </c>
@@ -8560,7 +12527,7 @@
         <v>6248777</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="5">
         <v>6000</v>
       </c>
@@ -8589,7 +12556,7 @@
         <v>8913611</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
         <v>7000</v>
       </c>
@@ -8618,7 +12585,7 @@
         <v>12248429</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="5">
         <v>8000</v>
       </c>
@@ -8647,7 +12614,7 @@
         <v>16014251</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="5">
         <v>9000</v>
       </c>
@@ -8676,7 +12643,7 @@
         <v>20256294</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="5">
         <v>10000</v>
       </c>
@@ -8705,7 +12672,7 @@
         <v>24983535</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="5">
         <v>11000</v>
       </c>
@@ -8734,7 +12701,7 @@
         <v>30136980</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="5">
         <v>12000</v>
       </c>
@@ -8763,7 +12730,7 @@
         <v>35840443</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="5">
         <v>13000</v>
       </c>
@@ -8792,7 +12759,7 @@
         <v>42266813</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16" s="5">
         <v>14000</v>
       </c>
@@ -8821,7 +12788,7 @@
         <v>49213127</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" s="5">
         <v>15000</v>
       </c>
@@ -8850,7 +12817,7 @@
         <v>56173382</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B18" s="5">
         <v>16000</v>
       </c>
@@ -8879,7 +12846,7 @@
         <v>63767799</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B19" s="5">
         <v>17000</v>
       </c>
@@ -8908,7 +12875,7 @@
         <v>71637344</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B20" s="5">
         <v>18000</v>
       </c>
@@ -8937,7 +12904,7 @@
         <v>81788313</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" s="5">
         <v>19000</v>
       </c>
@@ -8966,7 +12933,7 @@
         <v>90786727</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B22" s="5">
         <v>20000</v>
       </c>
@@ -8995,7 +12962,7 @@
         <v>100356039</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B23" s="5">
         <v>21000</v>
       </c>
@@ -9024,7 +12991,7 @@
         <v>109622884</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B24" s="5">
         <v>22000</v>
       </c>
@@ -9053,7 +13020,7 @@
         <v>120526108</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B25" s="5">
         <v>23000</v>
       </c>
@@ -9082,7 +13049,7 @@
         <v>132904918</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B26" s="5">
         <v>24000</v>
       </c>
@@ -9111,7 +13078,7 @@
         <v>142465310</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B27" s="5">
         <v>25000</v>
       </c>
@@ -9140,7 +13107,7 @@
         <v>156798968</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B28" s="5">
         <v>26000</v>
       </c>
@@ -9169,7 +13136,7 @@
         <v>169145282</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B29" s="5">
         <v>27000</v>
       </c>
@@ -9198,7 +13165,7 @@
         <v>182146714</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B30" s="5">
         <v>28000</v>
       </c>
@@ -9227,7 +13194,7 @@
         <v>195318306</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B31" s="5">
         <v>29000</v>
       </c>
@@ -9256,7 +13223,7 @@
         <v>210705580</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B32" s="5">
         <v>30000</v>
       </c>
@@ -9285,7 +13252,7 @@
         <v>224739171</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B33" s="5">
         <v>31000</v>
       </c>
@@ -9314,7 +13281,7 @@
         <v>239536305</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B34" s="5">
         <v>32000</v>
       </c>
@@ -9343,7 +13310,7 @@
         <v>256656273</v>
       </c>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B35" s="5">
         <v>33000</v>
       </c>
@@ -9372,7 +13339,7 @@
         <v>273302028</v>
       </c>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B36" s="5">
         <v>34000</v>
       </c>
@@ -9401,7 +13368,7 @@
         <v>287830632</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B37" s="5">
         <v>35000</v>
       </c>
@@ -9430,7 +13397,7 @@
         <v>306042453</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B38" s="5">
         <v>36000</v>
       </c>
@@ -9459,7 +13426,7 @@
         <v>322178034</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B39" s="5">
         <v>37000</v>
       </c>
@@ -9488,7 +13455,7 @@
         <v>339939858</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B40" s="5">
         <v>38000</v>
       </c>
@@ -9517,7 +13484,7 @@
         <v>361026451</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B41" s="5">
         <v>39000</v>
       </c>
@@ -9546,7 +13513,7 @@
         <v>381812999</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B42" s="5">
         <v>40000</v>
       </c>
@@ -9575,7 +13542,7 @@
         <v>400156642</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B43" s="5">
         <v>41000</v>
       </c>
@@ -9604,7 +13571,7 @@
         <v>418615343</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B44" s="5">
         <v>42000</v>
       </c>
@@ -9633,7 +13600,7 @@
         <v>440532444</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B45" s="5">
         <v>43000</v>
       </c>
@@ -9662,7 +13629,7 @@
         <v>463651393</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B46" s="5">
         <v>44000</v>
       </c>
@@ -9691,7 +13658,7 @@
         <v>485078102</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B47" s="5">
         <v>45000</v>
       </c>
@@ -9720,7 +13687,7 @@
         <v>507483302</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B48" s="5">
         <v>46000</v>
       </c>
@@ -9749,7 +13716,7 @@
         <v>529722103</v>
       </c>
     </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B49" s="5">
         <v>47000</v>
       </c>
@@ -9778,7 +13745,7 @@
         <v>551712814</v>
       </c>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B50" s="5">
         <v>48000</v>
       </c>
@@ -9807,7 +13774,7 @@
         <v>576594855</v>
       </c>
     </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B51" s="5">
         <v>49000</v>
       </c>
@@ -9836,7 +13803,7 @@
         <v>599241798</v>
       </c>
     </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B52" s="5">
         <v>50000</v>
       </c>
@@ -9865,7 +13832,7 @@
         <v>622883019</v>
       </c>
     </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.25">
       <c r="G53" s="1"/>
     </row>
   </sheetData>
@@ -9885,7 +13852,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A87ACB9-CF06-423F-9837-A7824A87C93F}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -9895,17 +13862,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2AC8A97-DDBA-4DB0-949A-D7A6A2EC5799}">
   <dimension ref="B1:L53"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
@@ -9922,7 +13889,7 @@
       <c r="K1" s="8"/>
       <c r="L1" s="8"/>
     </row>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -9951,7 +13918,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="5">
         <v>1000</v>
       </c>
@@ -9980,7 +13947,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="5">
         <v>2000</v>
       </c>
@@ -10009,7 +13976,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="5">
         <v>3000</v>
       </c>
@@ -10038,7 +14005,7 @@
         <v>2999</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="5">
         <v>4000</v>
       </c>
@@ -10067,7 +14034,7 @@
         <v>3999</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
         <v>5000</v>
       </c>
@@ -10096,7 +14063,7 @@
         <v>4999</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="5">
         <v>6000</v>
       </c>
@@ -10125,7 +14092,7 @@
         <v>5999</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
         <v>7000</v>
       </c>
@@ -10154,7 +14121,7 @@
         <v>6999</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="5">
         <v>8000</v>
       </c>
@@ -10183,7 +14150,7 @@
         <v>7999</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="5">
         <v>9000</v>
       </c>
@@ -10212,7 +14179,7 @@
         <v>8999</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="5">
         <v>10000</v>
       </c>
@@ -10241,7 +14208,7 @@
         <v>9999</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="5">
         <v>11000</v>
       </c>
@@ -10270,7 +14237,7 @@
         <v>10999</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="5">
         <v>12000</v>
       </c>
@@ -10299,7 +14266,7 @@
         <v>11999</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="5">
         <v>13000</v>
       </c>
@@ -10328,7 +14295,7 @@
         <v>12999</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16" s="5">
         <v>14000</v>
       </c>
@@ -10357,7 +14324,7 @@
         <v>13999</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" s="5">
         <v>15000</v>
       </c>
@@ -10386,7 +14353,7 @@
         <v>14999</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B18" s="5">
         <v>16000</v>
       </c>
@@ -10415,7 +14382,7 @@
         <v>15999</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B19" s="5">
         <v>17000</v>
       </c>
@@ -10444,7 +14411,7 @@
         <v>16999</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B20" s="5">
         <v>18000</v>
       </c>
@@ -10473,7 +14440,7 @@
         <v>17999</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" s="5">
         <v>19000</v>
       </c>
@@ -10502,7 +14469,7 @@
         <v>18999</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B22" s="5">
         <v>20000</v>
       </c>
@@ -10531,7 +14498,7 @@
         <v>19999</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B23" s="5">
         <v>21000</v>
       </c>
@@ -10560,7 +14527,7 @@
         <v>20999</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B24" s="5">
         <v>22000</v>
       </c>
@@ -10589,7 +14556,7 @@
         <v>21999</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B25" s="5">
         <v>23000</v>
       </c>
@@ -10618,7 +14585,7 @@
         <v>22999</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B26" s="5">
         <v>24000</v>
       </c>
@@ -10647,7 +14614,7 @@
         <v>23999</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B27" s="5">
         <v>25000</v>
       </c>
@@ -10676,7 +14643,7 @@
         <v>24999</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B28" s="5">
         <v>26000</v>
       </c>
@@ -10705,7 +14672,7 @@
         <v>25999</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B29" s="5">
         <v>27000</v>
       </c>
@@ -10734,7 +14701,7 @@
         <v>26999</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B30" s="5">
         <v>28000</v>
       </c>
@@ -10763,7 +14730,7 @@
         <v>27999</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B31" s="5">
         <v>29000</v>
       </c>
@@ -10792,7 +14759,7 @@
         <v>28999</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B32" s="5">
         <v>30000</v>
       </c>
@@ -10821,7 +14788,7 @@
         <v>29999</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B33" s="5">
         <v>31000</v>
       </c>
@@ -10850,7 +14817,7 @@
         <v>30999</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B34" s="5">
         <v>32000</v>
       </c>
@@ -10879,7 +14846,7 @@
         <v>31999</v>
       </c>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B35" s="5">
         <v>33000</v>
       </c>
@@ -10908,7 +14875,7 @@
         <v>32999</v>
       </c>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B36" s="5">
         <v>34000</v>
       </c>
@@ -10937,7 +14904,7 @@
         <v>33999</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B37" s="5">
         <v>35000</v>
       </c>
@@ -10966,7 +14933,7 @@
         <v>34999</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B38" s="5">
         <v>36000</v>
       </c>
@@ -10995,7 +14962,7 @@
         <v>35999</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B39" s="5">
         <v>37000</v>
       </c>
@@ -11024,7 +14991,7 @@
         <v>36999</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B40" s="5">
         <v>38000</v>
       </c>
@@ -11053,7 +15020,7 @@
         <v>37999</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B41" s="5">
         <v>39000</v>
       </c>
@@ -11082,7 +15049,7 @@
         <v>38999</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B42" s="5">
         <v>40000</v>
       </c>
@@ -11111,7 +15078,7 @@
         <v>39999</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B43" s="5">
         <v>41000</v>
       </c>
@@ -11140,7 +15107,7 @@
         <v>40999</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B44" s="5">
         <v>42000</v>
       </c>
@@ -11169,7 +15136,7 @@
         <v>41999</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B45" s="5">
         <v>43000</v>
       </c>
@@ -11198,7 +15165,7 @@
         <v>42999</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B46" s="5">
         <v>44000</v>
       </c>
@@ -11227,7 +15194,7 @@
         <v>43999</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B47" s="5">
         <v>45000</v>
       </c>
@@ -11256,7 +15223,7 @@
         <v>44999</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B48" s="5">
         <v>46000</v>
       </c>
@@ -11285,7 +15252,7 @@
         <v>45999</v>
       </c>
     </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B49" s="5">
         <v>47000</v>
       </c>
@@ -11314,7 +15281,7 @@
         <v>46999</v>
       </c>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B50" s="5">
         <v>48000</v>
       </c>
@@ -11343,7 +15310,7 @@
         <v>47999</v>
       </c>
     </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B51" s="5">
         <v>49000</v>
       </c>
@@ -11372,7 +15339,7 @@
         <v>48999</v>
       </c>
     </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B52" s="5">
         <v>50000</v>
       </c>
@@ -11401,7 +15368,7 @@
         <v>4999</v>
       </c>
     </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.25">
       <c r="G53" s="1"/>
     </row>
   </sheetData>
@@ -11421,7 +15388,1543 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7F3347C-990F-4F42-BAAC-9CF0059C811E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0873EED-A4EE-43E6-ACD6-0AF26340E591}">
+  <dimension ref="B1:L53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="F1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="J1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+    </row>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B3" s="5">
+        <v>1000</v>
+      </c>
+      <c r="C3" s="7">
+        <v>2499</v>
+      </c>
+      <c r="D3" s="6">
+        <v>12973</v>
+      </c>
+      <c r="F3">
+        <v>1000</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1498500</v>
+      </c>
+      <c r="H3">
+        <v>500500</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1000</v>
+      </c>
+      <c r="K3" s="7">
+        <v>501498</v>
+      </c>
+      <c r="L3" s="6">
+        <v>500499</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B4" s="5">
+        <v>2000</v>
+      </c>
+      <c r="C4" s="7">
+        <v>4999</v>
+      </c>
+      <c r="D4" s="6">
+        <v>27949</v>
+      </c>
+      <c r="F4">
+        <v>2000</v>
+      </c>
+      <c r="G4" s="1">
+        <v>5997000</v>
+      </c>
+      <c r="H4">
+        <v>2001000</v>
+      </c>
+      <c r="J4" s="5">
+        <v>2000</v>
+      </c>
+      <c r="K4" s="7">
+        <v>2002998</v>
+      </c>
+      <c r="L4" s="6">
+        <v>2000999</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B5" s="5">
+        <v>3000</v>
+      </c>
+      <c r="C5" s="7">
+        <v>7499</v>
+      </c>
+      <c r="D5" s="6">
+        <v>43901</v>
+      </c>
+      <c r="F5">
+        <v>3000</v>
+      </c>
+      <c r="G5" s="1">
+        <v>13495500</v>
+      </c>
+      <c r="H5">
+        <v>4501500</v>
+      </c>
+      <c r="J5" s="5">
+        <v>3000</v>
+      </c>
+      <c r="K5" s="7">
+        <v>4504498</v>
+      </c>
+      <c r="L5" s="6">
+        <v>4501499</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B6" s="5">
+        <v>4000</v>
+      </c>
+      <c r="C6" s="7">
+        <v>9999</v>
+      </c>
+      <c r="D6" s="6">
+        <v>59901</v>
+      </c>
+      <c r="F6">
+        <v>4000</v>
+      </c>
+      <c r="G6" s="1">
+        <v>23994000</v>
+      </c>
+      <c r="H6">
+        <v>8002000</v>
+      </c>
+      <c r="J6" s="5">
+        <v>4000</v>
+      </c>
+      <c r="K6">
+        <v>8005998</v>
+      </c>
+      <c r="L6">
+        <v>8001999</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B7" s="5">
+        <v>5000</v>
+      </c>
+      <c r="C7" s="7">
+        <v>12499</v>
+      </c>
+      <c r="D7" s="6">
+        <v>76805</v>
+      </c>
+      <c r="F7">
+        <v>5000</v>
+      </c>
+      <c r="G7" s="1">
+        <v>37492500</v>
+      </c>
+      <c r="H7">
+        <v>12502500</v>
+      </c>
+      <c r="J7" s="5">
+        <v>5000</v>
+      </c>
+      <c r="K7">
+        <v>12507498</v>
+      </c>
+      <c r="L7">
+        <v>12502499</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B8" s="5">
+        <v>6000</v>
+      </c>
+      <c r="C8" s="7">
+        <v>14999</v>
+      </c>
+      <c r="D8" s="6">
+        <v>93805</v>
+      </c>
+      <c r="F8">
+        <v>6000</v>
+      </c>
+      <c r="G8" s="1">
+        <v>53991000</v>
+      </c>
+      <c r="H8">
+        <v>18003000</v>
+      </c>
+      <c r="J8" s="5">
+        <v>6000</v>
+      </c>
+      <c r="K8">
+        <v>18008998</v>
+      </c>
+      <c r="L8">
+        <v>18002999</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B9" s="5">
+        <v>7000</v>
+      </c>
+      <c r="C9" s="7">
+        <v>17499</v>
+      </c>
+      <c r="D9" s="6">
+        <v>110805</v>
+      </c>
+      <c r="F9">
+        <v>7000</v>
+      </c>
+      <c r="G9" s="1">
+        <v>73489500</v>
+      </c>
+      <c r="H9">
+        <v>24503500</v>
+      </c>
+      <c r="J9" s="5">
+        <v>7000</v>
+      </c>
+      <c r="K9">
+        <v>24510498</v>
+      </c>
+      <c r="L9">
+        <v>24503499</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B10" s="5">
+        <v>8000</v>
+      </c>
+      <c r="C10" s="7">
+        <v>19999</v>
+      </c>
+      <c r="D10" s="6">
+        <v>127805</v>
+      </c>
+      <c r="F10">
+        <v>8000</v>
+      </c>
+      <c r="G10" s="1">
+        <v>95988000</v>
+      </c>
+      <c r="H10">
+        <v>32004000</v>
+      </c>
+      <c r="J10" s="5">
+        <v>8000</v>
+      </c>
+      <c r="K10">
+        <v>32011998</v>
+      </c>
+      <c r="L10">
+        <v>32003999</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B11" s="5">
+        <v>9000</v>
+      </c>
+      <c r="C11" s="7">
+        <v>22499</v>
+      </c>
+      <c r="D11" s="6">
+        <v>145613</v>
+      </c>
+      <c r="F11">
+        <v>9000</v>
+      </c>
+      <c r="G11" s="1">
+        <v>121486500</v>
+      </c>
+      <c r="H11">
+        <v>40504500</v>
+      </c>
+      <c r="J11" s="5">
+        <v>9000</v>
+      </c>
+      <c r="K11">
+        <v>40513498</v>
+      </c>
+      <c r="L11">
+        <v>40504499</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B12" s="5">
+        <v>10000</v>
+      </c>
+      <c r="C12" s="7">
+        <v>24999</v>
+      </c>
+      <c r="D12" s="6">
+        <v>163613</v>
+      </c>
+      <c r="F12">
+        <v>10000</v>
+      </c>
+      <c r="G12" s="1">
+        <v>149985000</v>
+      </c>
+      <c r="H12">
+        <v>50005000</v>
+      </c>
+      <c r="J12" s="5">
+        <v>10000</v>
+      </c>
+      <c r="K12">
+        <v>50014998</v>
+      </c>
+      <c r="L12">
+        <v>50004999</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B13" s="5">
+        <v>11000</v>
+      </c>
+      <c r="C13" s="7">
+        <v>27499</v>
+      </c>
+      <c r="D13" s="6">
+        <v>181613</v>
+      </c>
+      <c r="F13">
+        <v>11000</v>
+      </c>
+      <c r="G13" s="1">
+        <v>181483500</v>
+      </c>
+      <c r="H13">
+        <v>60505500</v>
+      </c>
+      <c r="J13" s="5">
+        <v>11000</v>
+      </c>
+      <c r="K13">
+        <v>60516498</v>
+      </c>
+      <c r="L13">
+        <v>60505499</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B14" s="5">
+        <v>12000</v>
+      </c>
+      <c r="C14" s="7">
+        <v>29999</v>
+      </c>
+      <c r="D14" s="6">
+        <v>199613</v>
+      </c>
+      <c r="F14">
+        <v>12000</v>
+      </c>
+      <c r="G14" s="1">
+        <v>215982000</v>
+      </c>
+      <c r="H14">
+        <v>72006000</v>
+      </c>
+      <c r="J14" s="5">
+        <v>12000</v>
+      </c>
+      <c r="K14">
+        <v>72017998</v>
+      </c>
+      <c r="L14">
+        <v>72005999</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B15" s="5">
+        <v>13000</v>
+      </c>
+      <c r="C15" s="7">
+        <v>32499</v>
+      </c>
+      <c r="D15" s="6">
+        <v>217613</v>
+      </c>
+      <c r="F15">
+        <v>13000</v>
+      </c>
+      <c r="G15" s="1">
+        <v>253480500</v>
+      </c>
+      <c r="H15">
+        <v>84506500</v>
+      </c>
+      <c r="J15" s="5">
+        <v>13000</v>
+      </c>
+      <c r="K15">
+        <v>84519498</v>
+      </c>
+      <c r="L15">
+        <v>84506499</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B16" s="5">
+        <v>14000</v>
+      </c>
+      <c r="C16" s="7">
+        <v>34999</v>
+      </c>
+      <c r="D16" s="6">
+        <v>235613</v>
+      </c>
+      <c r="F16">
+        <v>14000</v>
+      </c>
+      <c r="G16" s="1">
+        <v>293979000</v>
+      </c>
+      <c r="H16">
+        <v>98007000</v>
+      </c>
+      <c r="J16" s="5">
+        <v>14000</v>
+      </c>
+      <c r="K16">
+        <v>98020998</v>
+      </c>
+      <c r="L16">
+        <v>98006999</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B17" s="5">
+        <v>15000</v>
+      </c>
+      <c r="C17" s="7">
+        <v>37499</v>
+      </c>
+      <c r="D17" s="6">
+        <v>253613</v>
+      </c>
+      <c r="F17">
+        <v>15000</v>
+      </c>
+      <c r="G17" s="1">
+        <v>337477500</v>
+      </c>
+      <c r="H17">
+        <v>112507500</v>
+      </c>
+      <c r="J17" s="5">
+        <v>15000</v>
+      </c>
+      <c r="K17">
+        <v>112522498</v>
+      </c>
+      <c r="L17">
+        <v>112507499</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B18" s="5">
+        <v>16000</v>
+      </c>
+      <c r="C18" s="7">
+        <v>39999</v>
+      </c>
+      <c r="D18" s="6">
+        <v>271613</v>
+      </c>
+      <c r="F18">
+        <v>16000</v>
+      </c>
+      <c r="G18" s="1">
+        <v>383976000</v>
+      </c>
+      <c r="H18">
+        <v>128008000</v>
+      </c>
+      <c r="J18" s="5">
+        <v>16000</v>
+      </c>
+      <c r="K18">
+        <v>128023998</v>
+      </c>
+      <c r="L18">
+        <v>128007999</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B19" s="5">
+        <v>17000</v>
+      </c>
+      <c r="C19" s="7">
+        <v>42499</v>
+      </c>
+      <c r="D19" s="6">
+        <v>290229</v>
+      </c>
+      <c r="F19">
+        <v>17000</v>
+      </c>
+      <c r="G19" s="1">
+        <v>433474500</v>
+      </c>
+      <c r="H19">
+        <v>144508500</v>
+      </c>
+      <c r="J19" s="5">
+        <v>17000</v>
+      </c>
+      <c r="K19">
+        <v>144525498</v>
+      </c>
+      <c r="L19">
+        <v>144508499</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B20" s="5">
+        <v>18000</v>
+      </c>
+      <c r="C20" s="7">
+        <v>44999</v>
+      </c>
+      <c r="D20" s="6">
+        <v>309229</v>
+      </c>
+      <c r="F20">
+        <v>18000</v>
+      </c>
+      <c r="G20" s="1">
+        <v>485973000</v>
+      </c>
+      <c r="H20">
+        <v>162009000</v>
+      </c>
+      <c r="J20" s="5">
+        <v>18000</v>
+      </c>
+      <c r="K20">
+        <v>162026998</v>
+      </c>
+      <c r="L20">
+        <v>162008999</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B21" s="5">
+        <v>19000</v>
+      </c>
+      <c r="C21" s="7">
+        <v>47499</v>
+      </c>
+      <c r="D21" s="6">
+        <v>328229</v>
+      </c>
+      <c r="F21">
+        <v>19000</v>
+      </c>
+      <c r="G21" s="1">
+        <v>541471500</v>
+      </c>
+      <c r="H21">
+        <v>180509500</v>
+      </c>
+      <c r="J21" s="5">
+        <v>19000</v>
+      </c>
+      <c r="K21">
+        <v>180528498</v>
+      </c>
+      <c r="L21">
+        <v>180509499</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B22" s="5">
+        <v>20000</v>
+      </c>
+      <c r="C22" s="7">
+        <v>49999</v>
+      </c>
+      <c r="D22" s="6">
+        <v>347229</v>
+      </c>
+      <c r="F22">
+        <v>20000</v>
+      </c>
+      <c r="G22" s="1">
+        <v>599970000</v>
+      </c>
+      <c r="H22">
+        <v>200010000</v>
+      </c>
+      <c r="J22" s="5">
+        <v>20000</v>
+      </c>
+      <c r="K22">
+        <v>200029998</v>
+      </c>
+      <c r="L22">
+        <v>200009999</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B23" s="5">
+        <v>21000</v>
+      </c>
+      <c r="C23" s="7">
+        <v>52499</v>
+      </c>
+      <c r="D23" s="6">
+        <v>366229</v>
+      </c>
+      <c r="F23">
+        <v>21000</v>
+      </c>
+      <c r="G23" s="1">
+        <v>661468500</v>
+      </c>
+      <c r="H23">
+        <v>220510500</v>
+      </c>
+      <c r="J23" s="5">
+        <v>21000</v>
+      </c>
+      <c r="K23">
+        <v>220531498</v>
+      </c>
+      <c r="L23">
+        <v>220510499</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B24" s="5">
+        <v>22000</v>
+      </c>
+      <c r="C24" s="7">
+        <v>54999</v>
+      </c>
+      <c r="D24" s="6">
+        <v>385229</v>
+      </c>
+      <c r="F24">
+        <v>22000</v>
+      </c>
+      <c r="G24" s="1">
+        <v>725967000</v>
+      </c>
+      <c r="H24">
+        <v>242011000</v>
+      </c>
+      <c r="J24" s="5">
+        <v>22000</v>
+      </c>
+      <c r="K24">
+        <v>242032998</v>
+      </c>
+      <c r="L24">
+        <v>242010999</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B25" s="5">
+        <v>23000</v>
+      </c>
+      <c r="C25" s="7">
+        <v>57499</v>
+      </c>
+      <c r="D25" s="6">
+        <v>404229</v>
+      </c>
+      <c r="F25">
+        <v>23000</v>
+      </c>
+      <c r="G25" s="1">
+        <v>793465500</v>
+      </c>
+      <c r="H25">
+        <v>264511500</v>
+      </c>
+      <c r="J25" s="5">
+        <v>23000</v>
+      </c>
+      <c r="K25">
+        <v>264534498</v>
+      </c>
+      <c r="L25">
+        <v>264511499</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B26" s="5">
+        <v>24000</v>
+      </c>
+      <c r="C26" s="7">
+        <v>59999</v>
+      </c>
+      <c r="D26" s="6">
+        <v>423229</v>
+      </c>
+      <c r="F26">
+        <v>24000</v>
+      </c>
+      <c r="G26" s="1">
+        <v>863964000</v>
+      </c>
+      <c r="H26">
+        <v>288012000</v>
+      </c>
+      <c r="J26" s="5">
+        <v>24000</v>
+      </c>
+      <c r="K26">
+        <v>288035998</v>
+      </c>
+      <c r="L26">
+        <v>288011999</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B27" s="5">
+        <v>25000</v>
+      </c>
+      <c r="C27" s="7">
+        <v>62499</v>
+      </c>
+      <c r="D27" s="6">
+        <v>442229</v>
+      </c>
+      <c r="F27">
+        <v>25000</v>
+      </c>
+      <c r="G27" s="1">
+        <v>937462500</v>
+      </c>
+      <c r="H27">
+        <v>312512500</v>
+      </c>
+      <c r="J27" s="5">
+        <v>25000</v>
+      </c>
+      <c r="K27">
+        <v>312537498</v>
+      </c>
+      <c r="L27">
+        <v>312512499</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B28" s="5">
+        <v>26000</v>
+      </c>
+      <c r="C28" s="7">
+        <v>64999</v>
+      </c>
+      <c r="D28" s="6">
+        <v>461229</v>
+      </c>
+      <c r="F28">
+        <v>26000</v>
+      </c>
+      <c r="G28" s="1">
+        <v>1013961000</v>
+      </c>
+      <c r="H28">
+        <v>338013000</v>
+      </c>
+      <c r="J28" s="5">
+        <v>26000</v>
+      </c>
+      <c r="K28">
+        <v>338038998</v>
+      </c>
+      <c r="L28">
+        <v>338012999</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B29" s="5">
+        <v>27000</v>
+      </c>
+      <c r="C29" s="7">
+        <v>67499</v>
+      </c>
+      <c r="D29" s="6">
+        <v>480229</v>
+      </c>
+      <c r="F29">
+        <v>27000</v>
+      </c>
+      <c r="G29" s="1">
+        <v>1093459500</v>
+      </c>
+      <c r="H29">
+        <v>364513500</v>
+      </c>
+      <c r="J29" s="5">
+        <v>27000</v>
+      </c>
+      <c r="K29">
+        <v>364540498</v>
+      </c>
+      <c r="L29">
+        <v>364513499</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B30" s="5">
+        <v>28000</v>
+      </c>
+      <c r="C30" s="7">
+        <v>69999</v>
+      </c>
+      <c r="D30" s="6">
+        <v>499229</v>
+      </c>
+      <c r="F30">
+        <v>28000</v>
+      </c>
+      <c r="G30" s="1">
+        <v>1175958000</v>
+      </c>
+      <c r="H30">
+        <v>392014000</v>
+      </c>
+      <c r="J30" s="5">
+        <v>28000</v>
+      </c>
+      <c r="K30">
+        <v>392041998</v>
+      </c>
+      <c r="L30">
+        <v>392013999</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B31" s="5">
+        <v>29000</v>
+      </c>
+      <c r="C31" s="7">
+        <v>72499</v>
+      </c>
+      <c r="D31" s="6">
+        <v>518229</v>
+      </c>
+      <c r="F31">
+        <v>29000</v>
+      </c>
+      <c r="G31" s="1">
+        <v>1261456500</v>
+      </c>
+      <c r="H31">
+        <v>420514500</v>
+      </c>
+      <c r="J31" s="5">
+        <v>29000</v>
+      </c>
+      <c r="K31">
+        <v>420543498</v>
+      </c>
+      <c r="L31">
+        <v>420514499</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B32" s="5">
+        <v>30000</v>
+      </c>
+      <c r="C32" s="7">
+        <v>74999</v>
+      </c>
+      <c r="D32" s="6">
+        <v>537229</v>
+      </c>
+      <c r="F32">
+        <v>30000</v>
+      </c>
+      <c r="G32" s="1">
+        <v>1349955000</v>
+      </c>
+      <c r="H32">
+        <v>450015000</v>
+      </c>
+      <c r="J32" s="5">
+        <v>30000</v>
+      </c>
+      <c r="K32">
+        <v>450044998</v>
+      </c>
+      <c r="L32">
+        <v>450014999</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B33" s="5">
+        <v>31000</v>
+      </c>
+      <c r="C33" s="7">
+        <v>77499</v>
+      </c>
+      <c r="D33" s="6">
+        <v>556229</v>
+      </c>
+      <c r="F33">
+        <v>31000</v>
+      </c>
+      <c r="G33" s="1">
+        <v>1441453500</v>
+      </c>
+      <c r="H33">
+        <v>480515500</v>
+      </c>
+      <c r="J33" s="5">
+        <v>31000</v>
+      </c>
+      <c r="K33">
+        <v>480546498</v>
+      </c>
+      <c r="L33">
+        <v>480515499</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B34" s="5">
+        <v>32000</v>
+      </c>
+      <c r="C34" s="7">
+        <v>79999</v>
+      </c>
+      <c r="D34" s="6">
+        <v>575229</v>
+      </c>
+      <c r="F34">
+        <v>32000</v>
+      </c>
+      <c r="G34" s="1">
+        <v>1535952000</v>
+      </c>
+      <c r="H34">
+        <v>512016000</v>
+      </c>
+      <c r="J34" s="5">
+        <v>32000</v>
+      </c>
+      <c r="K34">
+        <v>512047998</v>
+      </c>
+      <c r="L34">
+        <v>512015999</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B35" s="5">
+        <v>33000</v>
+      </c>
+      <c r="C35" s="7">
+        <v>82499</v>
+      </c>
+      <c r="D35" s="6">
+        <v>594461</v>
+      </c>
+      <c r="F35">
+        <v>33000</v>
+      </c>
+      <c r="G35" s="1">
+        <v>1633450500</v>
+      </c>
+      <c r="H35">
+        <v>544516500</v>
+      </c>
+      <c r="J35" s="5">
+        <v>33000</v>
+      </c>
+      <c r="K35">
+        <v>544549498</v>
+      </c>
+      <c r="L35">
+        <v>544516499</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B36" s="5">
+        <v>34000</v>
+      </c>
+      <c r="C36" s="7">
+        <v>84999</v>
+      </c>
+      <c r="D36" s="6">
+        <v>614461</v>
+      </c>
+      <c r="F36">
+        <v>34000</v>
+      </c>
+      <c r="G36" s="1">
+        <v>1733949000</v>
+      </c>
+      <c r="H36">
+        <v>578017000</v>
+      </c>
+      <c r="J36" s="5">
+        <v>34000</v>
+      </c>
+      <c r="K36">
+        <v>578050998</v>
+      </c>
+      <c r="L36">
+        <v>578016999</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B37" s="5">
+        <v>35000</v>
+      </c>
+      <c r="C37" s="7">
+        <v>87499</v>
+      </c>
+      <c r="D37" s="6">
+        <v>634461</v>
+      </c>
+      <c r="F37">
+        <v>35000</v>
+      </c>
+      <c r="G37" s="1">
+        <v>1837447500</v>
+      </c>
+      <c r="H37">
+        <v>612517500</v>
+      </c>
+      <c r="J37" s="5">
+        <v>35000</v>
+      </c>
+      <c r="K37">
+        <v>612552498</v>
+      </c>
+      <c r="L37">
+        <v>612517499</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B38" s="5">
+        <v>36000</v>
+      </c>
+      <c r="C38" s="7">
+        <v>89999</v>
+      </c>
+      <c r="D38" s="6">
+        <v>654461</v>
+      </c>
+      <c r="F38">
+        <v>36000</v>
+      </c>
+      <c r="G38" s="1">
+        <v>1943946000</v>
+      </c>
+      <c r="H38">
+        <v>648018000</v>
+      </c>
+      <c r="J38" s="5">
+        <v>36000</v>
+      </c>
+      <c r="K38">
+        <v>648053998</v>
+      </c>
+      <c r="L38">
+        <v>648017999</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B39" s="5">
+        <v>37000</v>
+      </c>
+      <c r="C39" s="7">
+        <v>92499</v>
+      </c>
+      <c r="D39" s="6">
+        <v>674461</v>
+      </c>
+      <c r="F39">
+        <v>37000</v>
+      </c>
+      <c r="G39" s="1">
+        <v>2053444500</v>
+      </c>
+      <c r="H39">
+        <v>684518500</v>
+      </c>
+      <c r="J39" s="5">
+        <v>37000</v>
+      </c>
+      <c r="K39">
+        <v>684555498</v>
+      </c>
+      <c r="L39">
+        <v>684518499</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B40" s="5">
+        <v>38000</v>
+      </c>
+      <c r="C40" s="7">
+        <v>94999</v>
+      </c>
+      <c r="D40" s="6">
+        <v>694461</v>
+      </c>
+      <c r="F40">
+        <v>38000</v>
+      </c>
+      <c r="G40" s="1">
+        <v>2165943000</v>
+      </c>
+      <c r="H40">
+        <v>722019000</v>
+      </c>
+      <c r="J40" s="5">
+        <v>38000</v>
+      </c>
+      <c r="K40">
+        <v>722056998</v>
+      </c>
+      <c r="L40">
+        <v>722018999</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B41" s="5">
+        <v>39000</v>
+      </c>
+      <c r="C41" s="7">
+        <v>97499</v>
+      </c>
+      <c r="D41" s="6">
+        <v>714461</v>
+      </c>
+      <c r="F41">
+        <v>39000</v>
+      </c>
+      <c r="G41" s="1">
+        <v>2281441500</v>
+      </c>
+      <c r="H41">
+        <v>760519500</v>
+      </c>
+      <c r="J41" s="5">
+        <v>39000</v>
+      </c>
+      <c r="K41">
+        <v>760558498</v>
+      </c>
+      <c r="L41">
+        <v>760519499</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B42" s="5">
+        <v>40000</v>
+      </c>
+      <c r="C42" s="7">
+        <v>99999</v>
+      </c>
+      <c r="D42" s="6">
+        <v>734461</v>
+      </c>
+      <c r="F42">
+        <v>40000</v>
+      </c>
+      <c r="G42" s="1">
+        <v>2399940000</v>
+      </c>
+      <c r="H42">
+        <v>800020000</v>
+      </c>
+      <c r="J42" s="5">
+        <v>40000</v>
+      </c>
+      <c r="K42">
+        <v>800059998</v>
+      </c>
+      <c r="L42">
+        <v>800019999</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B43" s="5">
+        <v>41000</v>
+      </c>
+      <c r="C43" s="7">
+        <v>102499</v>
+      </c>
+      <c r="D43" s="6">
+        <v>754461</v>
+      </c>
+      <c r="F43">
+        <v>41000</v>
+      </c>
+      <c r="G43" s="1">
+        <v>2521438500</v>
+      </c>
+      <c r="H43">
+        <v>840520500</v>
+      </c>
+      <c r="J43" s="5">
+        <v>41000</v>
+      </c>
+      <c r="K43">
+        <v>840561498</v>
+      </c>
+      <c r="L43">
+        <v>840520499</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B44" s="5">
+        <v>42000</v>
+      </c>
+      <c r="C44" s="7">
+        <v>104999</v>
+      </c>
+      <c r="D44" s="6">
+        <v>774461</v>
+      </c>
+      <c r="F44">
+        <v>42000</v>
+      </c>
+      <c r="G44" s="1">
+        <v>2645937000</v>
+      </c>
+      <c r="H44">
+        <v>882021000</v>
+      </c>
+      <c r="J44" s="5">
+        <v>42000</v>
+      </c>
+      <c r="K44">
+        <v>882062998</v>
+      </c>
+      <c r="L44">
+        <v>882020999</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B45" s="5">
+        <v>43000</v>
+      </c>
+      <c r="C45" s="7">
+        <v>107499</v>
+      </c>
+      <c r="D45" s="6">
+        <v>794461</v>
+      </c>
+      <c r="F45">
+        <v>43000</v>
+      </c>
+      <c r="G45" s="1">
+        <v>2773435500</v>
+      </c>
+      <c r="H45">
+        <v>924521500</v>
+      </c>
+      <c r="J45" s="5">
+        <v>43000</v>
+      </c>
+      <c r="K45">
+        <v>924564498</v>
+      </c>
+      <c r="L45">
+        <v>924521499</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B46" s="5">
+        <v>44000</v>
+      </c>
+      <c r="C46" s="7">
+        <v>109999</v>
+      </c>
+      <c r="D46" s="6">
+        <v>814461</v>
+      </c>
+      <c r="F46">
+        <v>44000</v>
+      </c>
+      <c r="G46" s="1">
+        <v>2903934000</v>
+      </c>
+      <c r="H46">
+        <v>968022000</v>
+      </c>
+      <c r="J46" s="5">
+        <v>44000</v>
+      </c>
+      <c r="K46">
+        <v>968065998</v>
+      </c>
+      <c r="L46">
+        <v>968021999</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B47" s="5">
+        <v>45000</v>
+      </c>
+      <c r="C47" s="7">
+        <v>112499</v>
+      </c>
+      <c r="D47" s="6">
+        <v>834461</v>
+      </c>
+      <c r="F47">
+        <v>45000</v>
+      </c>
+      <c r="G47" s="1">
+        <v>3037432500</v>
+      </c>
+      <c r="H47">
+        <v>1012522500</v>
+      </c>
+      <c r="J47" s="5">
+        <v>45000</v>
+      </c>
+      <c r="K47">
+        <v>1012567498</v>
+      </c>
+      <c r="L47">
+        <v>1012522499</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B48" s="5">
+        <v>46000</v>
+      </c>
+      <c r="C48" s="7">
+        <v>114999</v>
+      </c>
+      <c r="D48" s="6">
+        <v>854461</v>
+      </c>
+      <c r="F48">
+        <v>46000</v>
+      </c>
+      <c r="G48" s="1">
+        <v>3173931000</v>
+      </c>
+      <c r="H48">
+        <v>1058023000</v>
+      </c>
+      <c r="J48" s="5">
+        <v>46000</v>
+      </c>
+      <c r="K48">
+        <v>1058068998</v>
+      </c>
+      <c r="L48">
+        <v>1058022999</v>
+      </c>
+    </row>
+    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B49" s="5">
+        <v>47000</v>
+      </c>
+      <c r="C49" s="7">
+        <v>117499</v>
+      </c>
+      <c r="D49" s="6">
+        <v>874461</v>
+      </c>
+      <c r="F49">
+        <v>47000</v>
+      </c>
+      <c r="G49" s="1">
+        <v>3313429500</v>
+      </c>
+      <c r="H49">
+        <v>1104523500</v>
+      </c>
+      <c r="J49" s="5">
+        <v>47000</v>
+      </c>
+      <c r="K49">
+        <v>1104570498</v>
+      </c>
+      <c r="L49">
+        <v>1104523499</v>
+      </c>
+    </row>
+    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B50" s="5">
+        <v>48000</v>
+      </c>
+      <c r="C50" s="7">
+        <v>119999</v>
+      </c>
+      <c r="D50" s="6">
+        <v>894461</v>
+      </c>
+      <c r="F50">
+        <v>48000</v>
+      </c>
+      <c r="G50" s="1">
+        <v>3455928000</v>
+      </c>
+      <c r="H50">
+        <v>1152024000</v>
+      </c>
+      <c r="J50" s="5">
+        <v>48000</v>
+      </c>
+      <c r="K50">
+        <v>1152071998</v>
+      </c>
+      <c r="L50">
+        <v>1152023999</v>
+      </c>
+    </row>
+    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B51" s="5">
+        <v>49000</v>
+      </c>
+      <c r="C51" s="7">
+        <v>122499</v>
+      </c>
+      <c r="D51" s="6">
+        <v>914461</v>
+      </c>
+      <c r="F51">
+        <v>49000</v>
+      </c>
+      <c r="G51" s="1">
+        <v>3601426500</v>
+      </c>
+      <c r="H51">
+        <v>1200524500</v>
+      </c>
+      <c r="J51" s="5">
+        <v>49000</v>
+      </c>
+      <c r="K51">
+        <v>1200573498</v>
+      </c>
+      <c r="L51">
+        <v>1200524499</v>
+      </c>
+    </row>
+    <row r="52" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B52" s="5">
+        <v>50000</v>
+      </c>
+      <c r="C52" s="7">
+        <v>124999</v>
+      </c>
+      <c r="D52" s="6">
+        <v>934461</v>
+      </c>
+      <c r="F52">
+        <v>50000</v>
+      </c>
+      <c r="G52" s="1">
+        <v>3749925000</v>
+      </c>
+      <c r="H52">
+        <v>1250025000</v>
+      </c>
+      <c r="J52" s="5">
+        <v>50000</v>
+      </c>
+      <c r="K52">
+        <v>1250074998</v>
+      </c>
+      <c r="L52">
+        <v>1250024999</v>
+      </c>
+    </row>
+    <row r="53" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="G53" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="J1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="2">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E89D3CC-823F-4217-9FB5-CF53E4286503}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/exp2.xlsx
+++ b/exp2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Algs_and_data_structures\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\3sem_git\Algs_and_data_structures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD5D19A8-316B-440B-9F2C-1D21839DDA5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D2CF9A9-4288-4264-B29F-2ADABE7EB74C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="random" sheetId="1" r:id="rId1"/>
@@ -97,7 +97,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -136,11 +136,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -152,11 +161,60 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="18">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -11991,11 +12049,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{12DBA126-0BED-484C-AA50-D6AE7A611FC4}" name="Таблица7367" displayName="Таблица7367" ref="F2:H53" totalsRowShown="0">
-  <autoFilter ref="F2:H53" xr:uid="{12DBA126-0BED-484C-AA50-D6AE7A611FC4}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{12DBA126-0BED-484C-AA50-D6AE7A611FC4}" name="Таблица7367" displayName="Таблица7367" ref="F2:H52" totalsRowShown="0">
+  <autoFilter ref="F2:H52" xr:uid="{12DBA126-0BED-484C-AA50-D6AE7A611FC4}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{609707E7-BB94-42A5-917D-9570B5AC7EEF}" name="N"/>
-    <tableColumn id="2" xr3:uid="{65B1B6C8-8ACD-417E-A7A0-594CC47A6D37}" name="Copy sh" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{65B1B6C8-8ACD-417E-A7A0-594CC47A6D37}" name="Copy sh" dataDxfId="17"/>
     <tableColumn id="3" xr3:uid="{F893E8C0-37FA-4D96-8689-B68BE51E2DFE}" name="Compare sh"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -12003,23 +12061,23 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{3A419A4E-1F00-42E1-A1D0-7871938F171F}" name="Таблица7" displayName="Таблица7" ref="B2:D52" totalsRowShown="0" tableBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{3A419A4E-1F00-42E1-A1D0-7871938F171F}" name="Таблица7" displayName="Таблица7" ref="B2:D52" totalsRowShown="0" tableBorderDxfId="16">
   <autoFilter ref="B2:D52" xr:uid="{3A419A4E-1F00-42E1-A1D0-7871938F171F}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{C1BDC60F-4A13-494C-A180-955CEE5697F5}" name="N" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{1B7691C3-923C-4E01-92E9-BAD16478DB72}" name="Copy q" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{DE5D2A1C-D75F-491A-98D0-A233B66BB08C}" name="Compare q" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{C1BDC60F-4A13-494C-A180-955CEE5697F5}" name="N" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{1B7691C3-923C-4E01-92E9-BAD16478DB72}" name="Copy q" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{DE5D2A1C-D75F-491A-98D0-A233B66BB08C}" name="Compare q" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5607FA58-C544-441A-8987-5BE2B0F172ED}" name="Таблица73672" displayName="Таблица73672" ref="F2:H53" totalsRowShown="0">
-  <autoFilter ref="F2:H53" xr:uid="{5607FA58-C544-441A-8987-5BE2B0F172ED}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5607FA58-C544-441A-8987-5BE2B0F172ED}" name="Таблица73672" displayName="Таблица73672" ref="F2:H52" totalsRowShown="0">
+  <autoFilter ref="F2:H52" xr:uid="{5607FA58-C544-441A-8987-5BE2B0F172ED}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{ACEAB66B-AE32-45A2-8926-84E6302C5E34}" name="N"/>
-    <tableColumn id="2" xr3:uid="{11DAFB21-07B3-48E3-908A-5CFC4A1D1B33}" name="Copy sh" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{11DAFB21-07B3-48E3-908A-5CFC4A1D1B33}" name="Copy sh" dataDxfId="12"/>
     <tableColumn id="3" xr3:uid="{53077772-C28F-4257-85A8-0AB505F9C552}" name="Compare sh"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -12027,23 +12085,23 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{79971A81-4FD2-4594-8052-CC4F7D0125A7}" name="Таблица73" displayName="Таблица73" ref="B2:D52" totalsRowShown="0" tableBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{79971A81-4FD2-4594-8052-CC4F7D0125A7}" name="Таблица73" displayName="Таблица73" ref="B2:D52" totalsRowShown="0" tableBorderDxfId="11">
   <autoFilter ref="B2:D52" xr:uid="{79971A81-4FD2-4594-8052-CC4F7D0125A7}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{FEE85231-2D90-4F77-A4C5-25EA4911F4D0}" name="N" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{A2D10756-2042-4755-9BE2-14696913FBBE}" name="Copy q" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{24984630-59D9-464B-AB12-390715BE809E}" name="Compare q" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{FEE85231-2D90-4F77-A4C5-25EA4911F4D0}" name="N" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{A2D10756-2042-4755-9BE2-14696913FBBE}" name="Copy q" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{24984630-59D9-464B-AB12-390715BE809E}" name="Compare q" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{ED744B51-A767-4A8E-B9D0-0D74B7E8AAE2}" name="Таблица73674" displayName="Таблица73674" ref="F2:H53" totalsRowShown="0">
-  <autoFilter ref="F2:H53" xr:uid="{ED744B51-A767-4A8E-B9D0-0D74B7E8AAE2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{ED744B51-A767-4A8E-B9D0-0D74B7E8AAE2}" name="Таблица73674" displayName="Таблица73674" ref="F2:H52" totalsRowShown="0">
+  <autoFilter ref="F2:H52" xr:uid="{ED744B51-A767-4A8E-B9D0-0D74B7E8AAE2}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{3F088BB7-E2AB-4740-8A11-CB8A7500598F}" name="N"/>
-    <tableColumn id="2" xr3:uid="{93D673C7-E911-4D6E-8346-FB7A0A7688F4}" name="Copy sh" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{93D673C7-E911-4D6E-8346-FB7A0A7688F4}" name="Copy sh" dataDxfId="7"/>
     <tableColumn id="3" xr3:uid="{3724D42B-91E7-4801-B2A7-9EB7767D914C}" name="Compare sh"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -12051,12 +12109,24 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{19C91100-B377-4295-B55E-A294CE197BAF}" name="Таблица75" displayName="Таблица75" ref="B2:D52" totalsRowShown="0" tableBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{19C91100-B377-4295-B55E-A294CE197BAF}" name="Таблица75" displayName="Таблица75" ref="B2:D52" totalsRowShown="0" tableBorderDxfId="6">
   <autoFilter ref="B2:D52" xr:uid="{19C91100-B377-4295-B55E-A294CE197BAF}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{179A060F-CEF4-4233-842D-7560B1E84EA1}" name="N" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{C94038B0-6362-4C5E-BB84-74E87A8F8E1F}" name="Copy q" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{F5C1EFA1-AFAD-41AD-A8AD-009468CCF1F9}" name="Compare q" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{179A060F-CEF4-4233-842D-7560B1E84EA1}" name="N" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{C94038B0-6362-4C5E-BB84-74E87A8F8E1F}" name="Copy q" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{F5C1EFA1-AFAD-41AD-A8AD-009468CCF1F9}" name="Compare q" dataDxfId="3"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{1D3BD2E5-13FB-4C69-B4CB-392001DF7D21}" name="Таблица5" displayName="Таблица5" ref="J2:L52" totalsRowShown="0" headerRowDxfId="0" tableBorderDxfId="2">
+  <autoFilter ref="J2:L52" xr:uid="{1D3BD2E5-13FB-4C69-B4CB-392001DF7D21}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{853468BE-2CEE-408C-B6AC-522559D3DA44}" name="N" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{20F60E0B-D056-47C3-9D68-526C6E274666}" name="Copy ins"/>
+    <tableColumn id="3" xr3:uid="{FEDA7734-8BF0-4D39-AF9C-DE61911382F1}" name="Compare ins"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12326,17 +12396,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:L53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
@@ -12353,7 +12423,7 @@
       <c r="K1" s="8"/>
       <c r="L1" s="8"/>
     </row>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -12382,7 +12452,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="5">
         <v>1000</v>
       </c>
@@ -12411,7 +12481,7 @@
         <v>251381</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" s="5">
         <v>2000</v>
       </c>
@@ -12440,7 +12510,7 @@
         <v>960933</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="5">
         <v>3000</v>
       </c>
@@ -12469,7 +12539,7 @@
         <v>2218307</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="5">
         <v>4000</v>
       </c>
@@ -12498,7 +12568,7 @@
         <v>3989996</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="5">
         <v>5000</v>
       </c>
@@ -12527,7 +12597,7 @@
         <v>6248777</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="5">
         <v>6000</v>
       </c>
@@ -12556,7 +12626,7 @@
         <v>8913611</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="5">
         <v>7000</v>
       </c>
@@ -12585,7 +12655,7 @@
         <v>12248429</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="5">
         <v>8000</v>
       </c>
@@ -12614,7 +12684,7 @@
         <v>16014251</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="5">
         <v>9000</v>
       </c>
@@ -12643,7 +12713,7 @@
         <v>20256294</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="5">
         <v>10000</v>
       </c>
@@ -12672,7 +12742,7 @@
         <v>24983535</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="5">
         <v>11000</v>
       </c>
@@ -12701,7 +12771,7 @@
         <v>30136980</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="5">
         <v>12000</v>
       </c>
@@ -12730,7 +12800,7 @@
         <v>35840443</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="5">
         <v>13000</v>
       </c>
@@ -12759,7 +12829,7 @@
         <v>42266813</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="5">
         <v>14000</v>
       </c>
@@ -12788,7 +12858,7 @@
         <v>49213127</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="5">
         <v>15000</v>
       </c>
@@ -12817,7 +12887,7 @@
         <v>56173382</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="5">
         <v>16000</v>
       </c>
@@ -12846,7 +12916,7 @@
         <v>63767799</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="5">
         <v>17000</v>
       </c>
@@ -12875,7 +12945,7 @@
         <v>71637344</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="5">
         <v>18000</v>
       </c>
@@ -12904,7 +12974,7 @@
         <v>81788313</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="5">
         <v>19000</v>
       </c>
@@ -12933,7 +13003,7 @@
         <v>90786727</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="5">
         <v>20000</v>
       </c>
@@ -12962,7 +13032,7 @@
         <v>100356039</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="5">
         <v>21000</v>
       </c>
@@ -12991,7 +13061,7 @@
         <v>109622884</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="5">
         <v>22000</v>
       </c>
@@ -13020,7 +13090,7 @@
         <v>120526108</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="5">
         <v>23000</v>
       </c>
@@ -13049,7 +13119,7 @@
         <v>132904918</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="5">
         <v>24000</v>
       </c>
@@ -13078,7 +13148,7 @@
         <v>142465310</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" s="5">
         <v>25000</v>
       </c>
@@ -13107,7 +13177,7 @@
         <v>156798968</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" s="5">
         <v>26000</v>
       </c>
@@ -13136,7 +13206,7 @@
         <v>169145282</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" s="5">
         <v>27000</v>
       </c>
@@ -13165,7 +13235,7 @@
         <v>182146714</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30" s="5">
         <v>28000</v>
       </c>
@@ -13194,7 +13264,7 @@
         <v>195318306</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31" s="5">
         <v>29000</v>
       </c>
@@ -13223,7 +13293,7 @@
         <v>210705580</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" s="5">
         <v>30000</v>
       </c>
@@ -13252,7 +13322,7 @@
         <v>224739171</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B33" s="5">
         <v>31000</v>
       </c>
@@ -13281,7 +13351,7 @@
         <v>239536305</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B34" s="5">
         <v>32000</v>
       </c>
@@ -13310,7 +13380,7 @@
         <v>256656273</v>
       </c>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" s="5">
         <v>33000</v>
       </c>
@@ -13339,7 +13409,7 @@
         <v>273302028</v>
       </c>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B36" s="5">
         <v>34000</v>
       </c>
@@ -13368,7 +13438,7 @@
         <v>287830632</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B37" s="5">
         <v>35000</v>
       </c>
@@ -13397,7 +13467,7 @@
         <v>306042453</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B38" s="5">
         <v>36000</v>
       </c>
@@ -13426,7 +13496,7 @@
         <v>322178034</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B39" s="5">
         <v>37000</v>
       </c>
@@ -13455,7 +13525,7 @@
         <v>339939858</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B40" s="5">
         <v>38000</v>
       </c>
@@ -13484,7 +13554,7 @@
         <v>361026451</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B41" s="5">
         <v>39000</v>
       </c>
@@ -13513,7 +13583,7 @@
         <v>381812999</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B42" s="5">
         <v>40000</v>
       </c>
@@ -13542,7 +13612,7 @@
         <v>400156642</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B43" s="5">
         <v>41000</v>
       </c>
@@ -13571,7 +13641,7 @@
         <v>418615343</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B44" s="5">
         <v>42000</v>
       </c>
@@ -13600,7 +13670,7 @@
         <v>440532444</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B45" s="5">
         <v>43000</v>
       </c>
@@ -13629,7 +13699,7 @@
         <v>463651393</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B46" s="5">
         <v>44000</v>
       </c>
@@ -13658,7 +13728,7 @@
         <v>485078102</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B47" s="5">
         <v>45000</v>
       </c>
@@ -13687,7 +13757,7 @@
         <v>507483302</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B48" s="5">
         <v>46000</v>
       </c>
@@ -13716,7 +13786,7 @@
         <v>529722103</v>
       </c>
     </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B49" s="5">
         <v>47000</v>
       </c>
@@ -13745,7 +13815,7 @@
         <v>551712814</v>
       </c>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B50" s="5">
         <v>48000</v>
       </c>
@@ -13774,7 +13844,7 @@
         <v>576594855</v>
       </c>
     </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B51" s="5">
         <v>49000</v>
       </c>
@@ -13803,7 +13873,7 @@
         <v>599241798</v>
       </c>
     </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B52" s="5">
         <v>50000</v>
       </c>
@@ -13832,7 +13902,7 @@
         <v>622883019</v>
       </c>
     </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.3">
       <c r="G53" s="1"/>
     </row>
   </sheetData>
@@ -13852,7 +13922,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A87ACB9-CF06-423F-9837-A7824A87C93F}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -13862,17 +13932,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2AC8A97-DDBA-4DB0-949A-D7A6A2EC5799}">
   <dimension ref="B1:L53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
@@ -13889,7 +13959,7 @@
       <c r="K1" s="8"/>
       <c r="L1" s="8"/>
     </row>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -13918,7 +13988,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="5">
         <v>1000</v>
       </c>
@@ -13947,7 +14017,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" s="5">
         <v>2000</v>
       </c>
@@ -13976,7 +14046,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="5">
         <v>3000</v>
       </c>
@@ -14005,7 +14075,7 @@
         <v>2999</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="5">
         <v>4000</v>
       </c>
@@ -14034,7 +14104,7 @@
         <v>3999</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="5">
         <v>5000</v>
       </c>
@@ -14063,7 +14133,7 @@
         <v>4999</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="5">
         <v>6000</v>
       </c>
@@ -14092,7 +14162,7 @@
         <v>5999</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="5">
         <v>7000</v>
       </c>
@@ -14121,7 +14191,7 @@
         <v>6999</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="5">
         <v>8000</v>
       </c>
@@ -14150,7 +14220,7 @@
         <v>7999</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="5">
         <v>9000</v>
       </c>
@@ -14179,7 +14249,7 @@
         <v>8999</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="5">
         <v>10000</v>
       </c>
@@ -14208,7 +14278,7 @@
         <v>9999</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="5">
         <v>11000</v>
       </c>
@@ -14237,7 +14307,7 @@
         <v>10999</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="5">
         <v>12000</v>
       </c>
@@ -14266,7 +14336,7 @@
         <v>11999</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="5">
         <v>13000</v>
       </c>
@@ -14295,7 +14365,7 @@
         <v>12999</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="5">
         <v>14000</v>
       </c>
@@ -14324,7 +14394,7 @@
         <v>13999</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="5">
         <v>15000</v>
       </c>
@@ -14353,7 +14423,7 @@
         <v>14999</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="5">
         <v>16000</v>
       </c>
@@ -14382,7 +14452,7 @@
         <v>15999</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="5">
         <v>17000</v>
       </c>
@@ -14411,7 +14481,7 @@
         <v>16999</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="5">
         <v>18000</v>
       </c>
@@ -14440,7 +14510,7 @@
         <v>17999</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="5">
         <v>19000</v>
       </c>
@@ -14469,7 +14539,7 @@
         <v>18999</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="5">
         <v>20000</v>
       </c>
@@ -14498,7 +14568,7 @@
         <v>19999</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="5">
         <v>21000</v>
       </c>
@@ -14527,7 +14597,7 @@
         <v>20999</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="5">
         <v>22000</v>
       </c>
@@ -14556,7 +14626,7 @@
         <v>21999</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="5">
         <v>23000</v>
       </c>
@@ -14585,7 +14655,7 @@
         <v>22999</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="5">
         <v>24000</v>
       </c>
@@ -14614,7 +14684,7 @@
         <v>23999</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" s="5">
         <v>25000</v>
       </c>
@@ -14643,7 +14713,7 @@
         <v>24999</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" s="5">
         <v>26000</v>
       </c>
@@ -14672,7 +14742,7 @@
         <v>25999</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" s="5">
         <v>27000</v>
       </c>
@@ -14701,7 +14771,7 @@
         <v>26999</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30" s="5">
         <v>28000</v>
       </c>
@@ -14730,7 +14800,7 @@
         <v>27999</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31" s="5">
         <v>29000</v>
       </c>
@@ -14759,7 +14829,7 @@
         <v>28999</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" s="5">
         <v>30000</v>
       </c>
@@ -14788,7 +14858,7 @@
         <v>29999</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B33" s="5">
         <v>31000</v>
       </c>
@@ -14817,7 +14887,7 @@
         <v>30999</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B34" s="5">
         <v>32000</v>
       </c>
@@ -14846,7 +14916,7 @@
         <v>31999</v>
       </c>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" s="5">
         <v>33000</v>
       </c>
@@ -14875,7 +14945,7 @@
         <v>32999</v>
       </c>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B36" s="5">
         <v>34000</v>
       </c>
@@ -14904,7 +14974,7 @@
         <v>33999</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B37" s="5">
         <v>35000</v>
       </c>
@@ -14933,7 +15003,7 @@
         <v>34999</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B38" s="5">
         <v>36000</v>
       </c>
@@ -14962,7 +15032,7 @@
         <v>35999</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B39" s="5">
         <v>37000</v>
       </c>
@@ -14991,7 +15061,7 @@
         <v>36999</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B40" s="5">
         <v>38000</v>
       </c>
@@ -15020,7 +15090,7 @@
         <v>37999</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B41" s="5">
         <v>39000</v>
       </c>
@@ -15049,7 +15119,7 @@
         <v>38999</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B42" s="5">
         <v>40000</v>
       </c>
@@ -15078,7 +15148,7 @@
         <v>39999</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B43" s="5">
         <v>41000</v>
       </c>
@@ -15107,7 +15177,7 @@
         <v>40999</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B44" s="5">
         <v>42000</v>
       </c>
@@ -15136,7 +15206,7 @@
         <v>41999</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B45" s="5">
         <v>43000</v>
       </c>
@@ -15165,7 +15235,7 @@
         <v>42999</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B46" s="5">
         <v>44000</v>
       </c>
@@ -15194,7 +15264,7 @@
         <v>43999</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B47" s="5">
         <v>45000</v>
       </c>
@@ -15223,7 +15293,7 @@
         <v>44999</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B48" s="5">
         <v>46000</v>
       </c>
@@ -15252,7 +15322,7 @@
         <v>45999</v>
       </c>
     </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B49" s="5">
         <v>47000</v>
       </c>
@@ -15281,7 +15351,7 @@
         <v>46999</v>
       </c>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B50" s="5">
         <v>48000</v>
       </c>
@@ -15310,7 +15380,7 @@
         <v>47999</v>
       </c>
     </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B51" s="5">
         <v>49000</v>
       </c>
@@ -15339,7 +15409,7 @@
         <v>48999</v>
       </c>
     </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B52" s="5">
         <v>50000</v>
       </c>
@@ -15368,7 +15438,7 @@
         <v>4999</v>
       </c>
     </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.3">
       <c r="G53" s="1"/>
     </row>
   </sheetData>
@@ -15388,7 +15458,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7F3347C-990F-4F42-BAAC-9CF0059C811E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -15398,17 +15468,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0873EED-A4EE-43E6-ACD6-0AF26340E591}">
   <dimension ref="B1:L53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="12" max="12" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
@@ -15425,7 +15497,7 @@
       <c r="K1" s="8"/>
       <c r="L1" s="8"/>
     </row>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -15444,17 +15516,17 @@
       <c r="H2" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="5">
         <v>1000</v>
       </c>
@@ -15473,7 +15545,7 @@
       <c r="H3">
         <v>500500</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3" s="9">
         <v>1000</v>
       </c>
       <c r="K3" s="7">
@@ -15483,7 +15555,7 @@
         <v>500499</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" s="5">
         <v>2000</v>
       </c>
@@ -15502,7 +15574,7 @@
       <c r="H4">
         <v>2001000</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="9">
         <v>2000</v>
       </c>
       <c r="K4" s="7">
@@ -15512,7 +15584,7 @@
         <v>2000999</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="5">
         <v>3000</v>
       </c>
@@ -15531,7 +15603,7 @@
       <c r="H5">
         <v>4501500</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="9">
         <v>3000</v>
       </c>
       <c r="K5" s="7">
@@ -15541,7 +15613,7 @@
         <v>4501499</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="5">
         <v>4000</v>
       </c>
@@ -15560,7 +15632,7 @@
       <c r="H6">
         <v>8002000</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="9">
         <v>4000</v>
       </c>
       <c r="K6">
@@ -15570,7 +15642,7 @@
         <v>8001999</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="5">
         <v>5000</v>
       </c>
@@ -15589,7 +15661,7 @@
       <c r="H7">
         <v>12502500</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7" s="9">
         <v>5000</v>
       </c>
       <c r="K7">
@@ -15599,7 +15671,7 @@
         <v>12502499</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="5">
         <v>6000</v>
       </c>
@@ -15618,7 +15690,7 @@
       <c r="H8">
         <v>18003000</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8" s="9">
         <v>6000</v>
       </c>
       <c r="K8">
@@ -15628,7 +15700,7 @@
         <v>18002999</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="5">
         <v>7000</v>
       </c>
@@ -15647,7 +15719,7 @@
       <c r="H9">
         <v>24503500</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="9">
         <v>7000</v>
       </c>
       <c r="K9">
@@ -15657,7 +15729,7 @@
         <v>24503499</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="5">
         <v>8000</v>
       </c>
@@ -15676,7 +15748,7 @@
       <c r="H10">
         <v>32004000</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="9">
         <v>8000</v>
       </c>
       <c r="K10">
@@ -15686,7 +15758,7 @@
         <v>32003999</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="5">
         <v>9000</v>
       </c>
@@ -15705,7 +15777,7 @@
       <c r="H11">
         <v>40504500</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11" s="9">
         <v>9000</v>
       </c>
       <c r="K11">
@@ -15715,7 +15787,7 @@
         <v>40504499</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="5">
         <v>10000</v>
       </c>
@@ -15734,7 +15806,7 @@
       <c r="H12">
         <v>50005000</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12" s="9">
         <v>10000</v>
       </c>
       <c r="K12">
@@ -15744,7 +15816,7 @@
         <v>50004999</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="5">
         <v>11000</v>
       </c>
@@ -15763,7 +15835,7 @@
       <c r="H13">
         <v>60505500</v>
       </c>
-      <c r="J13" s="5">
+      <c r="J13" s="9">
         <v>11000</v>
       </c>
       <c r="K13">
@@ -15773,7 +15845,7 @@
         <v>60505499</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="5">
         <v>12000</v>
       </c>
@@ -15792,7 +15864,7 @@
       <c r="H14">
         <v>72006000</v>
       </c>
-      <c r="J14" s="5">
+      <c r="J14" s="9">
         <v>12000</v>
       </c>
       <c r="K14">
@@ -15802,7 +15874,7 @@
         <v>72005999</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="5">
         <v>13000</v>
       </c>
@@ -15821,7 +15893,7 @@
       <c r="H15">
         <v>84506500</v>
       </c>
-      <c r="J15" s="5">
+      <c r="J15" s="9">
         <v>13000</v>
       </c>
       <c r="K15">
@@ -15831,7 +15903,7 @@
         <v>84506499</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="5">
         <v>14000</v>
       </c>
@@ -15850,7 +15922,7 @@
       <c r="H16">
         <v>98007000</v>
       </c>
-      <c r="J16" s="5">
+      <c r="J16" s="9">
         <v>14000</v>
       </c>
       <c r="K16">
@@ -15860,7 +15932,7 @@
         <v>98006999</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="5">
         <v>15000</v>
       </c>
@@ -15879,7 +15951,7 @@
       <c r="H17">
         <v>112507500</v>
       </c>
-      <c r="J17" s="5">
+      <c r="J17" s="9">
         <v>15000</v>
       </c>
       <c r="K17">
@@ -15889,7 +15961,7 @@
         <v>112507499</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="5">
         <v>16000</v>
       </c>
@@ -15908,7 +15980,7 @@
       <c r="H18">
         <v>128008000</v>
       </c>
-      <c r="J18" s="5">
+      <c r="J18" s="9">
         <v>16000</v>
       </c>
       <c r="K18">
@@ -15918,7 +15990,7 @@
         <v>128007999</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="5">
         <v>17000</v>
       </c>
@@ -15937,7 +16009,7 @@
       <c r="H19">
         <v>144508500</v>
       </c>
-      <c r="J19" s="5">
+      <c r="J19" s="9">
         <v>17000</v>
       </c>
       <c r="K19">
@@ -15947,7 +16019,7 @@
         <v>144508499</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="5">
         <v>18000</v>
       </c>
@@ -15966,7 +16038,7 @@
       <c r="H20">
         <v>162009000</v>
       </c>
-      <c r="J20" s="5">
+      <c r="J20" s="9">
         <v>18000</v>
       </c>
       <c r="K20">
@@ -15976,7 +16048,7 @@
         <v>162008999</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="5">
         <v>19000</v>
       </c>
@@ -15995,7 +16067,7 @@
       <c r="H21">
         <v>180509500</v>
       </c>
-      <c r="J21" s="5">
+      <c r="J21" s="9">
         <v>19000</v>
       </c>
       <c r="K21">
@@ -16005,7 +16077,7 @@
         <v>180509499</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="5">
         <v>20000</v>
       </c>
@@ -16024,7 +16096,7 @@
       <c r="H22">
         <v>200010000</v>
       </c>
-      <c r="J22" s="5">
+      <c r="J22" s="9">
         <v>20000</v>
       </c>
       <c r="K22">
@@ -16034,7 +16106,7 @@
         <v>200009999</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="5">
         <v>21000</v>
       </c>
@@ -16053,7 +16125,7 @@
       <c r="H23">
         <v>220510500</v>
       </c>
-      <c r="J23" s="5">
+      <c r="J23" s="9">
         <v>21000</v>
       </c>
       <c r="K23">
@@ -16063,7 +16135,7 @@
         <v>220510499</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="5">
         <v>22000</v>
       </c>
@@ -16082,7 +16154,7 @@
       <c r="H24">
         <v>242011000</v>
       </c>
-      <c r="J24" s="5">
+      <c r="J24" s="9">
         <v>22000</v>
       </c>
       <c r="K24">
@@ -16092,7 +16164,7 @@
         <v>242010999</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="5">
         <v>23000</v>
       </c>
@@ -16111,7 +16183,7 @@
       <c r="H25">
         <v>264511500</v>
       </c>
-      <c r="J25" s="5">
+      <c r="J25" s="9">
         <v>23000</v>
       </c>
       <c r="K25">
@@ -16121,7 +16193,7 @@
         <v>264511499</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="5">
         <v>24000</v>
       </c>
@@ -16140,7 +16212,7 @@
       <c r="H26">
         <v>288012000</v>
       </c>
-      <c r="J26" s="5">
+      <c r="J26" s="9">
         <v>24000</v>
       </c>
       <c r="K26">
@@ -16150,7 +16222,7 @@
         <v>288011999</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" s="5">
         <v>25000</v>
       </c>
@@ -16169,7 +16241,7 @@
       <c r="H27">
         <v>312512500</v>
       </c>
-      <c r="J27" s="5">
+      <c r="J27" s="9">
         <v>25000</v>
       </c>
       <c r="K27">
@@ -16179,7 +16251,7 @@
         <v>312512499</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" s="5">
         <v>26000</v>
       </c>
@@ -16198,7 +16270,7 @@
       <c r="H28">
         <v>338013000</v>
       </c>
-      <c r="J28" s="5">
+      <c r="J28" s="9">
         <v>26000</v>
       </c>
       <c r="K28">
@@ -16208,7 +16280,7 @@
         <v>338012999</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" s="5">
         <v>27000</v>
       </c>
@@ -16227,7 +16299,7 @@
       <c r="H29">
         <v>364513500</v>
       </c>
-      <c r="J29" s="5">
+      <c r="J29" s="9">
         <v>27000</v>
       </c>
       <c r="K29">
@@ -16237,7 +16309,7 @@
         <v>364513499</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30" s="5">
         <v>28000</v>
       </c>
@@ -16256,7 +16328,7 @@
       <c r="H30">
         <v>392014000</v>
       </c>
-      <c r="J30" s="5">
+      <c r="J30" s="9">
         <v>28000</v>
       </c>
       <c r="K30">
@@ -16266,7 +16338,7 @@
         <v>392013999</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31" s="5">
         <v>29000</v>
       </c>
@@ -16285,7 +16357,7 @@
       <c r="H31">
         <v>420514500</v>
       </c>
-      <c r="J31" s="5">
+      <c r="J31" s="9">
         <v>29000</v>
       </c>
       <c r="K31">
@@ -16295,7 +16367,7 @@
         <v>420514499</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" s="5">
         <v>30000</v>
       </c>
@@ -16314,7 +16386,7 @@
       <c r="H32">
         <v>450015000</v>
       </c>
-      <c r="J32" s="5">
+      <c r="J32" s="9">
         <v>30000</v>
       </c>
       <c r="K32">
@@ -16324,7 +16396,7 @@
         <v>450014999</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B33" s="5">
         <v>31000</v>
       </c>
@@ -16343,7 +16415,7 @@
       <c r="H33">
         <v>480515500</v>
       </c>
-      <c r="J33" s="5">
+      <c r="J33" s="9">
         <v>31000</v>
       </c>
       <c r="K33">
@@ -16353,7 +16425,7 @@
         <v>480515499</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B34" s="5">
         <v>32000</v>
       </c>
@@ -16372,7 +16444,7 @@
       <c r="H34">
         <v>512016000</v>
       </c>
-      <c r="J34" s="5">
+      <c r="J34" s="9">
         <v>32000</v>
       </c>
       <c r="K34">
@@ -16382,7 +16454,7 @@
         <v>512015999</v>
       </c>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" s="5">
         <v>33000</v>
       </c>
@@ -16401,7 +16473,7 @@
       <c r="H35">
         <v>544516500</v>
       </c>
-      <c r="J35" s="5">
+      <c r="J35" s="9">
         <v>33000</v>
       </c>
       <c r="K35">
@@ -16411,7 +16483,7 @@
         <v>544516499</v>
       </c>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B36" s="5">
         <v>34000</v>
       </c>
@@ -16430,7 +16502,7 @@
       <c r="H36">
         <v>578017000</v>
       </c>
-      <c r="J36" s="5">
+      <c r="J36" s="9">
         <v>34000</v>
       </c>
       <c r="K36">
@@ -16440,7 +16512,7 @@
         <v>578016999</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B37" s="5">
         <v>35000</v>
       </c>
@@ -16459,7 +16531,7 @@
       <c r="H37">
         <v>612517500</v>
       </c>
-      <c r="J37" s="5">
+      <c r="J37" s="9">
         <v>35000</v>
       </c>
       <c r="K37">
@@ -16469,7 +16541,7 @@
         <v>612517499</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B38" s="5">
         <v>36000</v>
       </c>
@@ -16488,7 +16560,7 @@
       <c r="H38">
         <v>648018000</v>
       </c>
-      <c r="J38" s="5">
+      <c r="J38" s="9">
         <v>36000</v>
       </c>
       <c r="K38">
@@ -16498,7 +16570,7 @@
         <v>648017999</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B39" s="5">
         <v>37000</v>
       </c>
@@ -16517,7 +16589,7 @@
       <c r="H39">
         <v>684518500</v>
       </c>
-      <c r="J39" s="5">
+      <c r="J39" s="9">
         <v>37000</v>
       </c>
       <c r="K39">
@@ -16527,7 +16599,7 @@
         <v>684518499</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B40" s="5">
         <v>38000</v>
       </c>
@@ -16546,7 +16618,7 @@
       <c r="H40">
         <v>722019000</v>
       </c>
-      <c r="J40" s="5">
+      <c r="J40" s="9">
         <v>38000</v>
       </c>
       <c r="K40">
@@ -16556,7 +16628,7 @@
         <v>722018999</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B41" s="5">
         <v>39000</v>
       </c>
@@ -16575,7 +16647,7 @@
       <c r="H41">
         <v>760519500</v>
       </c>
-      <c r="J41" s="5">
+      <c r="J41" s="9">
         <v>39000</v>
       </c>
       <c r="K41">
@@ -16585,7 +16657,7 @@
         <v>760519499</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B42" s="5">
         <v>40000</v>
       </c>
@@ -16604,7 +16676,7 @@
       <c r="H42">
         <v>800020000</v>
       </c>
-      <c r="J42" s="5">
+      <c r="J42" s="9">
         <v>40000</v>
       </c>
       <c r="K42">
@@ -16614,7 +16686,7 @@
         <v>800019999</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B43" s="5">
         <v>41000</v>
       </c>
@@ -16633,7 +16705,7 @@
       <c r="H43">
         <v>840520500</v>
       </c>
-      <c r="J43" s="5">
+      <c r="J43" s="9">
         <v>41000</v>
       </c>
       <c r="K43">
@@ -16643,7 +16715,7 @@
         <v>840520499</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B44" s="5">
         <v>42000</v>
       </c>
@@ -16662,7 +16734,7 @@
       <c r="H44">
         <v>882021000</v>
       </c>
-      <c r="J44" s="5">
+      <c r="J44" s="9">
         <v>42000</v>
       </c>
       <c r="K44">
@@ -16672,7 +16744,7 @@
         <v>882020999</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B45" s="5">
         <v>43000</v>
       </c>
@@ -16691,7 +16763,7 @@
       <c r="H45">
         <v>924521500</v>
       </c>
-      <c r="J45" s="5">
+      <c r="J45" s="9">
         <v>43000</v>
       </c>
       <c r="K45">
@@ -16701,7 +16773,7 @@
         <v>924521499</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B46" s="5">
         <v>44000</v>
       </c>
@@ -16720,7 +16792,7 @@
       <c r="H46">
         <v>968022000</v>
       </c>
-      <c r="J46" s="5">
+      <c r="J46" s="9">
         <v>44000</v>
       </c>
       <c r="K46">
@@ -16730,7 +16802,7 @@
         <v>968021999</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B47" s="5">
         <v>45000</v>
       </c>
@@ -16749,7 +16821,7 @@
       <c r="H47">
         <v>1012522500</v>
       </c>
-      <c r="J47" s="5">
+      <c r="J47" s="9">
         <v>45000</v>
       </c>
       <c r="K47">
@@ -16759,7 +16831,7 @@
         <v>1012522499</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B48" s="5">
         <v>46000</v>
       </c>
@@ -16778,7 +16850,7 @@
       <c r="H48">
         <v>1058023000</v>
       </c>
-      <c r="J48" s="5">
+      <c r="J48" s="9">
         <v>46000</v>
       </c>
       <c r="K48">
@@ -16788,7 +16860,7 @@
         <v>1058022999</v>
       </c>
     </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B49" s="5">
         <v>47000</v>
       </c>
@@ -16807,7 +16879,7 @@
       <c r="H49">
         <v>1104523500</v>
       </c>
-      <c r="J49" s="5">
+      <c r="J49" s="9">
         <v>47000</v>
       </c>
       <c r="K49">
@@ -16817,7 +16889,7 @@
         <v>1104523499</v>
       </c>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B50" s="5">
         <v>48000</v>
       </c>
@@ -16836,7 +16908,7 @@
       <c r="H50">
         <v>1152024000</v>
       </c>
-      <c r="J50" s="5">
+      <c r="J50" s="9">
         <v>48000</v>
       </c>
       <c r="K50">
@@ -16846,7 +16918,7 @@
         <v>1152023999</v>
       </c>
     </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B51" s="5">
         <v>49000</v>
       </c>
@@ -16865,7 +16937,7 @@
       <c r="H51">
         <v>1200524500</v>
       </c>
-      <c r="J51" s="5">
+      <c r="J51" s="9">
         <v>49000</v>
       </c>
       <c r="K51">
@@ -16875,7 +16947,7 @@
         <v>1200524499</v>
       </c>
     </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B52" s="5">
         <v>50000</v>
       </c>
@@ -16894,7 +16966,7 @@
       <c r="H52">
         <v>1250025000</v>
       </c>
-      <c r="J52" s="5">
+      <c r="J52" s="9">
         <v>50000</v>
       </c>
       <c r="K52">
@@ -16904,7 +16976,7 @@
         <v>1250024999</v>
       </c>
     </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.3">
       <c r="G53" s="1"/>
     </row>
   </sheetData>
@@ -16914,9 +16986,10 @@
     <mergeCell ref="J1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="2">
+  <tableParts count="3">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
@@ -16924,7 +16997,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E89D3CC-823F-4217-9FB5-CF53E4286503}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
